--- a/projects/minus-lock-system/MinusLock_Percent_Grid_Calculator.xlsx
+++ b/projects/minus-lock-system/MinusLock_Percent_Grid_Calculator.xlsx
@@ -13,6 +13,14 @@
     <sheet name="Summary" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Checks" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Manual" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="MarketModel" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="AdaptiveEngine" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="MarginControl" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="MonteCarlo" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="EquityModel" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="RecoveryMap" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="StressTest" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="RiskDashboard" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="LevelRange">Settings!$A$22:$A$200</definedName>
@@ -181,7 +189,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Raw vs Rounded Lots</a:t>
+              <a:t>Equity Curve</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -193,11 +201,6 @@
         <ser>
           <idx val="0"/>
           <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'DownTrend'!V2</f>
-            </strRef>
-          </tx>
           <spPr>
             <a:ln>
               <a:prstDash val="solid"/>
@@ -213,23 +216,18 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DownTrend'!$A$3:$A$8</f>
+              <f>'EquityModel'!$A$4:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DownTrend'!$V$3:$V$8</f>
+              <f>'EquityModel'!$B$3:$B$10</f>
             </numRef>
           </val>
         </ser>
         <ser>
           <idx val="1"/>
           <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'DownTrend'!W2</f>
-            </strRef>
-          </tx>
           <spPr>
             <a:ln>
               <a:prstDash val="solid"/>
@@ -245,23 +243,74 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DownTrend'!$A$3:$A$8</f>
+              <f>'EquityModel'!$A$4:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DownTrend'!$W$3:$W$8</f>
+              <f>'EquityModel'!$C$3:$C$10</f>
             </numRef>
           </val>
         </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>BreakEven Map</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
         <ser>
-          <idx val="2"/>
-          <order val="2"/>
-          <tx>
-            <strRef>
-              <f>'DownTrend'!X2</f>
-            </strRef>
-          </tx>
+          <idx val="0"/>
+          <order val="0"/>
           <spPr>
             <a:ln>
               <a:prstDash val="solid"/>
@@ -277,44 +326,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DownTrend'!$A$3:$A$8</f>
+              <f>'RecoveryMap'!$A$4:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DownTrend'!$X$3:$X$8</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="3"/>
-          <order val="3"/>
-          <tx>
-            <strRef>
-              <f>'DownTrend'!Y2</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'DownTrend'!$A$3:$A$8</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'DownTrend'!$Y$3:$Y$8</f>
+              <f>'RecoveryMap'!$B$3:$B$10</f>
             </numRef>
           </val>
         </ser>
@@ -365,7 +382,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>BUY/SELL after rounding</a:t>
+              <a:t>Floating DD</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -377,11 +394,6 @@
         <ser>
           <idx val="0"/>
           <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'DownTrend'!Q2</f>
-            </strRef>
-          </tx>
           <spPr>
             <a:ln>
               <a:prstDash val="solid"/>
@@ -397,44 +409,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DownTrend'!$A$3:$A$8</f>
+              <f>'EquityModel'!$A$4:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DownTrend'!$Q$3:$Q$8</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'DownTrend'!R2</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'DownTrend'!$A$3:$A$8</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'DownTrend'!$R$3:$R$8</f>
+              <f>'EquityModel'!$D$3:$D$10</f>
             </numRef>
           </val>
         </ser>
@@ -485,7 +465,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>SAFE adjustments count</a:t>
+              <a:t>Margin Load</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -497,11 +477,6 @@
         <ser>
           <idx val="0"/>
           <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'DownTrend'!AB2</f>
-            </strRef>
-          </tx>
           <spPr>
             <a:ln>
               <a:prstDash val="solid"/>
@@ -517,12 +492,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DownTrend'!$A$3:$A$8</f>
+              <f>'MarginControl'!$A$4:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DownTrend'!$AB$3:$AB$8</f>
+              <f>'MarginControl'!$M$3:$M$10</f>
             </numRef>
           </val>
         </ser>
@@ -573,7 +548,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Skew before/after</a:t>
+              <a:t>Skew Evolution</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -585,11 +560,6 @@
         <ser>
           <idx val="0"/>
           <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'DownTrend'!J2</f>
-            </strRef>
-          </tx>
           <spPr>
             <a:ln>
               <a:prstDash val="solid"/>
@@ -605,300 +575,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DownTrend'!$A$3:$A$8</f>
+              <f>'AdaptiveEngine'!$A$4:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DownTrend'!$J$3:$J$8</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'DownTrend'!K2</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'DownTrend'!$A$3:$A$8</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'DownTrend'!$K$3:$K$8</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="2"/>
-          <order val="2"/>
-          <tx>
-            <strRef>
-              <f>'DownTrend'!L2</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'DownTrend'!$A$3:$A$8</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'DownTrend'!$L$3:$L$8</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="3"/>
-          <order val="3"/>
-          <tx>
-            <strRef>
-              <f>'DownTrend'!M2</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'DownTrend'!$A$3:$A$8</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'DownTrend'!$M$3:$M$8</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="4"/>
-          <order val="4"/>
-          <tx>
-            <strRef>
-              <f>'DownTrend'!N2</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'DownTrend'!$A$3:$A$8</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'DownTrend'!$N$3:$N$8</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="5"/>
-          <order val="5"/>
-          <tx>
-            <strRef>
-              <f>'DownTrend'!O2</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'DownTrend'!$A$3:$A$8</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'DownTrend'!$O$3:$O$8</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="6"/>
-          <order val="6"/>
-          <tx>
-            <strRef>
-              <f>'DownTrend'!P2</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'DownTrend'!$A$3:$A$8</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'DownTrend'!$P$3:$P$8</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="7"/>
-          <order val="7"/>
-          <tx>
-            <strRef>
-              <f>'DownTrend'!Q2</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'DownTrend'!$A$3:$A$8</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'DownTrend'!$Q$3:$Q$8</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="8"/>
-          <order val="8"/>
-          <tx>
-            <strRef>
-              <f>'DownTrend'!R2</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'DownTrend'!$A$3:$A$8</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'DownTrend'!$R$3:$R$8</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="9"/>
-          <order val="9"/>
-          <tx>
-            <strRef>
-              <f>'DownTrend'!S2</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'DownTrend'!$A$3:$A$8</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'DownTrend'!$S$3:$S$8</f>
+              <f>'AdaptiveEngine'!$D$3:$D$10</f>
             </numRef>
           </val>
         </ser>
@@ -949,7 +631,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Skew after rounding</a:t>
+              <a:t>Compression Speed</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -961,11 +643,6 @@
         <ser>
           <idx val="0"/>
           <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'DownTrend'!S2</f>
-            </strRef>
-          </tx>
           <spPr>
             <a:ln>
               <a:prstDash val="solid"/>
@@ -981,12 +658,344 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DownTrend'!$A$3:$A$8</f>
+              <f>'RecoveryMap'!$A$4:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DownTrend'!$S$3:$S$8</f>
+              <f>'RecoveryMap'!$D$3:$D$10</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Recovery Probability</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'RiskDashboard'!$A$4:$A$10</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'RiskDashboard'!$E$3:$E$10</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>ATR Regime Step</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'MarketModel'!$A$4:$A$10</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'MarketModel'!$P$3:$P$10</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Risk Score</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'RiskDashboard'!$A$4:$A$10</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'RiskDashboard'!$B$3:$B$10</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Monte Carlo</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'MonteCarlo'!$A$4:$A$10</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'MonteCarlo'!$C$3:$C$10</f>
             </numRef>
           </val>
         </ser>
@@ -1132,6 +1141,116 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>60</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="6" name="Chart 6"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>72</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="7" name="Chart 7"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId7"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>84</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="8" name="Chart 8"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId8"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>96</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="9" name="Chart 9"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId9"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>108</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="10" name="Chart 10"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId10"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1720,6 +1839,867 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Monte Carlo Scenarios</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>Max DD</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>Max Levels</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>Margin Stress</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>Recovery Distance</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>Required Rollback</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>Survival</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Strong Downtrend</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>35</v>
+      </c>
+      <c r="C4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>850</v>
+      </c>
+      <c r="F4" t="n">
+        <v>420</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Strong Uptrend</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>33</v>
+      </c>
+      <c r="C5" t="n">
+        <v>8</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>820</v>
+      </c>
+      <c r="F5" t="n">
+        <v>400</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Volatile Trend</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>45</v>
+      </c>
+      <c r="C6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>DANGER</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F6" t="n">
+        <v>620</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Flash Crash</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>60</v>
+      </c>
+      <c r="C7" t="n">
+        <v>12</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1800</v>
+      </c>
+      <c r="F7" t="n">
+        <v>900</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Long Compression</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>28</v>
+      </c>
+      <c r="C8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>640</v>
+      </c>
+      <c r="F8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Endless Trend</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>72</v>
+      </c>
+      <c r="C9" t="n">
+        <v>14</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2600</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>VERY LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Trend + Spike</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>55</v>
+      </c>
+      <c r="C10" t="n">
+        <v>11</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>DANGER</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F10" t="n">
+        <v>760</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Equity Model</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>Balance</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>Floating DD</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>Margin Load</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0</v>
+      </c>
+      <c r="B4" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C4" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C5" t="n">
+        <v>9800</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>9500</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>20</v>
+      </c>
+      <c r="F6" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C7" t="n">
+        <v>9300</v>
+      </c>
+      <c r="D7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" t="n">
+        <v>35</v>
+      </c>
+      <c r="F7" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C8" t="n">
+        <v>9400</v>
+      </c>
+      <c r="D8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" t="n">
+        <v>50</v>
+      </c>
+      <c r="F8" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C9" t="n">
+        <v>9700</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>72</v>
+      </c>
+      <c r="F9" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C10" t="n">
+        <v>9950</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>90</v>
+      </c>
+      <c r="F10" t="n">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Recovery Map</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Level</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>RecoveryDistance</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>TimeBars</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>CompressionCycles</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>Basket&gt;=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="n">
+        <v>120</v>
+      </c>
+      <c r="C4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="n">
+        <v>260</v>
+      </c>
+      <c r="C5" t="n">
+        <v>16</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" t="n">
+        <v>430</v>
+      </c>
+      <c r="C6" t="n">
+        <v>28</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" t="n">
+        <v>660</v>
+      </c>
+      <c r="C7" t="n">
+        <v>45</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" t="n">
+        <v>980</v>
+      </c>
+      <c r="C8" t="n">
+        <v>70</v>
+      </c>
+      <c r="D8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1300</v>
+      </c>
+      <c r="C9" t="n">
+        <v>95</v>
+      </c>
+      <c r="D9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Stress Test</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ATR x2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ATR x5</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>DANGER</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Spread x3</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Gap 500</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>DANGER</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Flash move</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Infinite trend</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>No rollback</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Risk Dashboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>RiskScore</t>
+        </is>
+      </c>
+      <c r="B4">
+        <f>MIN(100,MAX(0,0.35*EquityModel!D6+0.35*MarginControl!B13+0.2*AdaptiveEngine!B2+0.1*MarketModel!B3/2))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>RiskStatus</t>
+        </is>
+      </c>
+      <c r="B5">
+        <f>IF(B4&lt;20,"SAFE",IF(B4&lt;40,"NORMAL",IF(B4&lt;60,"WARNING",IF(B4&lt;80,"DANGER","CRITICAL"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CurrentSkew</t>
+        </is>
+      </c>
+      <c r="B6">
+        <f>AdaptiveEngine!B2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SurvivalProbability</t>
+        </is>
+      </c>
+      <c r="B7">
+        <f>MAX(0,100-B4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AdaptiveLevelStop</t>
+        </is>
+      </c>
+      <c r="B8">
+        <f>IF(OR(MarginControl!B13&gt;70,EquityModel!D6&gt;25,MarketModel!B3&gt;200,AdaptiveEngine!D17&gt;25),"STOP NEW LEVELS","ALLOW")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -1742,7 +2722,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Big BUY %</t>
+          <t>Big %</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -1752,7 +2732,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Small SELL %</t>
+          <t>Small %</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -1817,7 +2797,7 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Total Opp %</t>
+          <t>Total Opposite %</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
@@ -1941,6 +2921,10 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C2&lt;0,E2&lt;0,J2&lt;0,AND(LEN(L2)&gt;0,L2&lt;0)),"ERROR: Negative input",IF(C2&lt;E2,"ERROR: Big BUY must be &gt;= Small SELL",IF(AND(LEN(L2)&gt;0,L2&gt;G2),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N2&lt;0,Q2&lt;0,R2&lt;0),"ERROR: Negative totals",IF(Q2&gt;R2,"ERROR: Rounding broke protection balance",IF(S2&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U2">
+        <f>IF(LEFT(T2,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
@@ -1960,11 +2944,11 @@
         <v>0</v>
       </c>
       <c r="AB2">
-        <f>IF(T2="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA2-Z2)&gt;1E-9),"FIXED",IF(ABS(S2)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T2,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA2-Z2)&gt;1E-9),"FIXED",IF(ABS(S2)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>IF(AB2="FIXED","Close adjusted by SAFE mode",IF(AB2="SAFE","Balance preserved",IF(AB2="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB2="FIXED","Close adjusted by SAFE mode",IF(AB2="SAFE","BUY/SELL balance preserved",IF(AB2="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -2047,12 +3031,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C3&lt;0,E3&lt;0,J3&lt;0,AND(LEN(L3)&gt;0,L3&lt;0)),"ERROR: Negative input",IF(C3&lt;E3,"ERROR: Big BUY must be &gt;= Small SELL",IF(AND(LEN(L3)&gt;0,L3&gt;G3),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N3&lt;0,Q3&lt;0,R3&lt;0),"ERROR: Negative totals",IF(Q3&gt;R3,"ERROR: Rounding broke protection balance",IF(S3&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U3">
+        <f>IF(LEFT(T3,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V3">
         <f>Settings!$B$2*C3/100</f>
         <v/>
       </c>
       <c r="W3">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V3,Settings!$B$5),V3),IF(Settings!$B$9,MROUND(V3,Settings!$B$5),V3))</f>
+        <f>IF(Settings!$B$9,FLOOR(V3,Settings!$B$5),V3)</f>
         <v/>
       </c>
       <c r="X3">
@@ -2060,7 +3048,7 @@
         <v/>
       </c>
       <c r="Y3">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X3,Settings!$B$5),X3),IF(Settings!$B$9,MROUND(X3,Settings!$B$5),X3))</f>
+        <f>IF(Settings!$B$9,CEILING(X3,Settings!$B$5),X3)</f>
         <v/>
       </c>
       <c r="Z3">
@@ -2072,11 +3060,11 @@
         <v/>
       </c>
       <c r="AB3">
-        <f>IF(T3="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA3-Z3)&gt;1E-9),"FIXED",IF(ABS(S3)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T3,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA3-Z3)&gt;1E-9),"FIXED",IF(ABS(S3)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>IF(AB3="FIXED","Close adjusted by SAFE mode",IF(AB3="SAFE","Balance preserved",IF(AB3="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB3="FIXED","Close adjusted by SAFE mode",IF(AB3="SAFE","BUY/SELL balance preserved",IF(AB3="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -2160,12 +3148,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C4&lt;0,E4&lt;0,J4&lt;0,AND(LEN(L4)&gt;0,L4&lt;0)),"ERROR: Negative input",IF(C4&lt;E4,"ERROR: Big BUY must be &gt;= Small SELL",IF(AND(LEN(L4)&gt;0,L4&gt;G4),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N4&lt;0,Q4&lt;0,R4&lt;0),"ERROR: Negative totals",IF(Q4&gt;R4,"ERROR: Rounding broke protection balance",IF(S4&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U4">
+        <f>IF(LEFT(T4,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V4">
         <f>Settings!$B$2*C4/100</f>
         <v/>
       </c>
       <c r="W4">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V4,Settings!$B$5),V4),IF(Settings!$B$9,MROUND(V4,Settings!$B$5),V4))</f>
+        <f>IF(Settings!$B$9,FLOOR(V4,Settings!$B$5),V4)</f>
         <v/>
       </c>
       <c r="X4">
@@ -2173,7 +3165,7 @@
         <v/>
       </c>
       <c r="Y4">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X4,Settings!$B$5),X4),IF(Settings!$B$9,MROUND(X4,Settings!$B$5),X4))</f>
+        <f>IF(Settings!$B$9,CEILING(X4,Settings!$B$5),X4)</f>
         <v/>
       </c>
       <c r="Z4">
@@ -2185,11 +3177,11 @@
         <v/>
       </c>
       <c r="AB4">
-        <f>IF(T4="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA4-Z4)&gt;1E-9),"FIXED",IF(ABS(S4)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T4,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA4-Z4)&gt;1E-9),"FIXED",IF(ABS(S4)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>IF(AB4="FIXED","Close adjusted by SAFE mode",IF(AB4="SAFE","Balance preserved",IF(AB4="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB4="FIXED","Close adjusted by SAFE mode",IF(AB4="SAFE","BUY/SELL balance preserved",IF(AB4="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -2273,12 +3265,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C5&lt;0,E5&lt;0,J5&lt;0,AND(LEN(L5)&gt;0,L5&lt;0)),"ERROR: Negative input",IF(C5&lt;E5,"ERROR: Big BUY must be &gt;= Small SELL",IF(AND(LEN(L5)&gt;0,L5&gt;G5),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N5&lt;0,Q5&lt;0,R5&lt;0),"ERROR: Negative totals",IF(Q5&gt;R5,"ERROR: Rounding broke protection balance",IF(S5&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U5">
+        <f>IF(LEFT(T5,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V5">
         <f>Settings!$B$2*C5/100</f>
         <v/>
       </c>
       <c r="W5">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V5,Settings!$B$5),V5),IF(Settings!$B$9,MROUND(V5,Settings!$B$5),V5))</f>
+        <f>IF(Settings!$B$9,FLOOR(V5,Settings!$B$5),V5)</f>
         <v/>
       </c>
       <c r="X5">
@@ -2286,7 +3282,7 @@
         <v/>
       </c>
       <c r="Y5">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X5,Settings!$B$5),X5),IF(Settings!$B$9,MROUND(X5,Settings!$B$5),X5))</f>
+        <f>IF(Settings!$B$9,CEILING(X5,Settings!$B$5),X5)</f>
         <v/>
       </c>
       <c r="Z5">
@@ -2298,11 +3294,11 @@
         <v/>
       </c>
       <c r="AB5">
-        <f>IF(T5="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA5-Z5)&gt;1E-9),"FIXED",IF(ABS(S5)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T5,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA5-Z5)&gt;1E-9),"FIXED",IF(ABS(S5)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>IF(AB5="FIXED","Close adjusted by SAFE mode",IF(AB5="SAFE","Balance preserved",IF(AB5="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB5="FIXED","Close adjusted by SAFE mode",IF(AB5="SAFE","BUY/SELL balance preserved",IF(AB5="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -2386,12 +3382,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C6&lt;0,E6&lt;0,J6&lt;0,AND(LEN(L6)&gt;0,L6&lt;0)),"ERROR: Negative input",IF(C6&lt;E6,"ERROR: Big BUY must be &gt;= Small SELL",IF(AND(LEN(L6)&gt;0,L6&gt;G6),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N6&lt;0,Q6&lt;0,R6&lt;0),"ERROR: Negative totals",IF(Q6&gt;R6,"ERROR: Rounding broke protection balance",IF(S6&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U6">
+        <f>IF(LEFT(T6,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V6">
         <f>Settings!$B$2*C6/100</f>
         <v/>
       </c>
       <c r="W6">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V6,Settings!$B$5),V6),IF(Settings!$B$9,MROUND(V6,Settings!$B$5),V6))</f>
+        <f>IF(Settings!$B$9,FLOOR(V6,Settings!$B$5),V6)</f>
         <v/>
       </c>
       <c r="X6">
@@ -2399,7 +3399,7 @@
         <v/>
       </c>
       <c r="Y6">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X6,Settings!$B$5),X6),IF(Settings!$B$9,MROUND(X6,Settings!$B$5),X6))</f>
+        <f>IF(Settings!$B$9,CEILING(X6,Settings!$B$5),X6)</f>
         <v/>
       </c>
       <c r="Z6">
@@ -2411,11 +3411,11 @@
         <v/>
       </c>
       <c r="AB6">
-        <f>IF(T6="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA6-Z6)&gt;1E-9),"FIXED",IF(ABS(S6)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T6,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA6-Z6)&gt;1E-9),"FIXED",IF(ABS(S6)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>IF(AB6="FIXED","Close adjusted by SAFE mode",IF(AB6="SAFE","Balance preserved",IF(AB6="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB6="FIXED","Close adjusted by SAFE mode",IF(AB6="SAFE","BUY/SELL balance preserved",IF(AB6="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -2499,12 +3499,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C7&lt;0,E7&lt;0,J7&lt;0,AND(LEN(L7)&gt;0,L7&lt;0)),"ERROR: Negative input",IF(C7&lt;E7,"ERROR: Big BUY must be &gt;= Small SELL",IF(AND(LEN(L7)&gt;0,L7&gt;G7),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N7&lt;0,Q7&lt;0,R7&lt;0),"ERROR: Negative totals",IF(Q7&gt;R7,"ERROR: Rounding broke protection balance",IF(S7&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U7">
+        <f>IF(LEFT(T7,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V7">
         <f>Settings!$B$2*C7/100</f>
         <v/>
       </c>
       <c r="W7">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V7,Settings!$B$5),V7),IF(Settings!$B$9,MROUND(V7,Settings!$B$5),V7))</f>
+        <f>IF(Settings!$B$9,FLOOR(V7,Settings!$B$5),V7)</f>
         <v/>
       </c>
       <c r="X7">
@@ -2512,7 +3516,7 @@
         <v/>
       </c>
       <c r="Y7">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X7,Settings!$B$5),X7),IF(Settings!$B$9,MROUND(X7,Settings!$B$5),X7))</f>
+        <f>IF(Settings!$B$9,CEILING(X7,Settings!$B$5),X7)</f>
         <v/>
       </c>
       <c r="Z7">
@@ -2524,11 +3528,11 @@
         <v/>
       </c>
       <c r="AB7">
-        <f>IF(T7="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA7-Z7)&gt;1E-9),"FIXED",IF(ABS(S7)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T7,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA7-Z7)&gt;1E-9),"FIXED",IF(ABS(S7)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>IF(AB7="FIXED","Close adjusted by SAFE mode",IF(AB7="SAFE","Balance preserved",IF(AB7="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB7="FIXED","Close adjusted by SAFE mode",IF(AB7="SAFE","BUY/SELL balance preserved",IF(AB7="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -2612,12 +3616,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C8&lt;0,E8&lt;0,J8&lt;0,AND(LEN(L8)&gt;0,L8&lt;0)),"ERROR: Negative input",IF(C8&lt;E8,"ERROR: Big BUY must be &gt;= Small SELL",IF(AND(LEN(L8)&gt;0,L8&gt;G8),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N8&lt;0,Q8&lt;0,R8&lt;0),"ERROR: Negative totals",IF(Q8&gt;R8,"ERROR: Rounding broke protection balance",IF(S8&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U8">
+        <f>IF(LEFT(T8,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V8">
         <f>Settings!$B$2*C8/100</f>
         <v/>
       </c>
       <c r="W8">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V8,Settings!$B$5),V8),IF(Settings!$B$9,MROUND(V8,Settings!$B$5),V8))</f>
+        <f>IF(Settings!$B$9,FLOOR(V8,Settings!$B$5),V8)</f>
         <v/>
       </c>
       <c r="X8">
@@ -2625,7 +3633,7 @@
         <v/>
       </c>
       <c r="Y8">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X8,Settings!$B$5),X8),IF(Settings!$B$9,MROUND(X8,Settings!$B$5),X8))</f>
+        <f>IF(Settings!$B$9,CEILING(X8,Settings!$B$5),X8)</f>
         <v/>
       </c>
       <c r="Z8">
@@ -2637,11 +3645,11 @@
         <v/>
       </c>
       <c r="AB8">
-        <f>IF(T8="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA8-Z8)&gt;1E-9),"FIXED",IF(ABS(S8)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T8,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA8-Z8)&gt;1E-9),"FIXED",IF(ABS(S8)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>IF(AB8="FIXED","Close adjusted by SAFE mode",IF(AB8="SAFE","Balance preserved",IF(AB8="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB8="FIXED","Close adjusted by SAFE mode",IF(AB8="SAFE","BUY/SELL balance preserved",IF(AB8="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -2725,12 +3733,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C9&lt;0,E9&lt;0,J9&lt;0,AND(LEN(L9)&gt;0,L9&lt;0)),"ERROR: Negative input",IF(C9&lt;E9,"ERROR: Big BUY must be &gt;= Small SELL",IF(AND(LEN(L9)&gt;0,L9&gt;G9),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N9&lt;0,Q9&lt;0,R9&lt;0),"ERROR: Negative totals",IF(Q9&gt;R9,"ERROR: Rounding broke protection balance",IF(S9&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U9">
+        <f>IF(LEFT(T9,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V9">
         <f>Settings!$B$2*C9/100</f>
         <v/>
       </c>
       <c r="W9">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V9,Settings!$B$5),V9),IF(Settings!$B$9,MROUND(V9,Settings!$B$5),V9))</f>
+        <f>IF(Settings!$B$9,FLOOR(V9,Settings!$B$5),V9)</f>
         <v/>
       </c>
       <c r="X9">
@@ -2738,7 +3750,7 @@
         <v/>
       </c>
       <c r="Y9">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X9,Settings!$B$5),X9),IF(Settings!$B$9,MROUND(X9,Settings!$B$5),X9))</f>
+        <f>IF(Settings!$B$9,CEILING(X9,Settings!$B$5),X9)</f>
         <v/>
       </c>
       <c r="Z9">
@@ -2750,11 +3762,11 @@
         <v/>
       </c>
       <c r="AB9">
-        <f>IF(T9="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA9-Z9)&gt;1E-9),"FIXED",IF(ABS(S9)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T9,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA9-Z9)&gt;1E-9),"FIXED",IF(ABS(S9)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>IF(AB9="FIXED","Close adjusted by SAFE mode",IF(AB9="SAFE","Balance preserved",IF(AB9="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB9="FIXED","Close adjusted by SAFE mode",IF(AB9="SAFE","BUY/SELL balance preserved",IF(AB9="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -2838,12 +3850,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C10&lt;0,E10&lt;0,J10&lt;0,AND(LEN(L10)&gt;0,L10&lt;0)),"ERROR: Negative input",IF(C10&lt;E10,"ERROR: Big BUY must be &gt;= Small SELL",IF(AND(LEN(L10)&gt;0,L10&gt;G10),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N10&lt;0,Q10&lt;0,R10&lt;0),"ERROR: Negative totals",IF(Q10&gt;R10,"ERROR: Rounding broke protection balance",IF(S10&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U10">
+        <f>IF(LEFT(T10,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V10">
         <f>Settings!$B$2*C10/100</f>
         <v/>
       </c>
       <c r="W10">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V10,Settings!$B$5),V10),IF(Settings!$B$9,MROUND(V10,Settings!$B$5),V10))</f>
+        <f>IF(Settings!$B$9,FLOOR(V10,Settings!$B$5),V10)</f>
         <v/>
       </c>
       <c r="X10">
@@ -2851,7 +3867,7 @@
         <v/>
       </c>
       <c r="Y10">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X10,Settings!$B$5),X10),IF(Settings!$B$9,MROUND(X10,Settings!$B$5),X10))</f>
+        <f>IF(Settings!$B$9,CEILING(X10,Settings!$B$5),X10)</f>
         <v/>
       </c>
       <c r="Z10">
@@ -2863,11 +3879,11 @@
         <v/>
       </c>
       <c r="AB10">
-        <f>IF(T10="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA10-Z10)&gt;1E-9),"FIXED",IF(ABS(S10)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T10,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA10-Z10)&gt;1E-9),"FIXED",IF(ABS(S10)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>IF(AB10="FIXED","Close adjusted by SAFE mode",IF(AB10="SAFE","Balance preserved",IF(AB10="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB10="FIXED","Close adjusted by SAFE mode",IF(AB10="SAFE","BUY/SELL balance preserved",IF(AB10="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -2951,12 +3967,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C11&lt;0,E11&lt;0,J11&lt;0,AND(LEN(L11)&gt;0,L11&lt;0)),"ERROR: Negative input",IF(C11&lt;E11,"ERROR: Big BUY must be &gt;= Small SELL",IF(AND(LEN(L11)&gt;0,L11&gt;G11),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N11&lt;0,Q11&lt;0,R11&lt;0),"ERROR: Negative totals",IF(Q11&gt;R11,"ERROR: Rounding broke protection balance",IF(S11&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U11">
+        <f>IF(LEFT(T11,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V11">
         <f>Settings!$B$2*C11/100</f>
         <v/>
       </c>
       <c r="W11">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V11,Settings!$B$5),V11),IF(Settings!$B$9,MROUND(V11,Settings!$B$5),V11))</f>
+        <f>IF(Settings!$B$9,FLOOR(V11,Settings!$B$5),V11)</f>
         <v/>
       </c>
       <c r="X11">
@@ -2964,7 +3984,7 @@
         <v/>
       </c>
       <c r="Y11">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X11,Settings!$B$5),X11),IF(Settings!$B$9,MROUND(X11,Settings!$B$5),X11))</f>
+        <f>IF(Settings!$B$9,CEILING(X11,Settings!$B$5),X11)</f>
         <v/>
       </c>
       <c r="Z11">
@@ -2976,11 +3996,11 @@
         <v/>
       </c>
       <c r="AB11">
-        <f>IF(T11="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA11-Z11)&gt;1E-9),"FIXED",IF(ABS(S11)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T11,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA11-Z11)&gt;1E-9),"FIXED",IF(ABS(S11)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>IF(AB11="FIXED","Close adjusted by SAFE mode",IF(AB11="SAFE","Balance preserved",IF(AB11="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB11="FIXED","Close adjusted by SAFE mode",IF(AB11="SAFE","BUY/SELL balance preserved",IF(AB11="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -3064,12 +4084,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C12&lt;0,E12&lt;0,J12&lt;0,AND(LEN(L12)&gt;0,L12&lt;0)),"ERROR: Negative input",IF(C12&lt;E12,"ERROR: Big BUY must be &gt;= Small SELL",IF(AND(LEN(L12)&gt;0,L12&gt;G12),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N12&lt;0,Q12&lt;0,R12&lt;0),"ERROR: Negative totals",IF(Q12&gt;R12,"ERROR: Rounding broke protection balance",IF(S12&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U12">
+        <f>IF(LEFT(T12,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V12">
         <f>Settings!$B$2*C12/100</f>
         <v/>
       </c>
       <c r="W12">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V12,Settings!$B$5),V12),IF(Settings!$B$9,MROUND(V12,Settings!$B$5),V12))</f>
+        <f>IF(Settings!$B$9,FLOOR(V12,Settings!$B$5),V12)</f>
         <v/>
       </c>
       <c r="X12">
@@ -3077,7 +4101,7 @@
         <v/>
       </c>
       <c r="Y12">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X12,Settings!$B$5),X12),IF(Settings!$B$9,MROUND(X12,Settings!$B$5),X12))</f>
+        <f>IF(Settings!$B$9,CEILING(X12,Settings!$B$5),X12)</f>
         <v/>
       </c>
       <c r="Z12">
@@ -3089,11 +4113,11 @@
         <v/>
       </c>
       <c r="AB12">
-        <f>IF(T12="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA12-Z12)&gt;1E-9),"FIXED",IF(ABS(S12)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T12,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA12-Z12)&gt;1E-9),"FIXED",IF(ABS(S12)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>IF(AB12="FIXED","Close adjusted by SAFE mode",IF(AB12="SAFE","Balance preserved",IF(AB12="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB12="FIXED","Close adjusted by SAFE mode",IF(AB12="SAFE","BUY/SELL balance preserved",IF(AB12="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -3177,12 +4201,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C13&lt;0,E13&lt;0,J13&lt;0,AND(LEN(L13)&gt;0,L13&lt;0)),"ERROR: Negative input",IF(C13&lt;E13,"ERROR: Big BUY must be &gt;= Small SELL",IF(AND(LEN(L13)&gt;0,L13&gt;G13),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N13&lt;0,Q13&lt;0,R13&lt;0),"ERROR: Negative totals",IF(Q13&gt;R13,"ERROR: Rounding broke protection balance",IF(S13&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U13">
+        <f>IF(LEFT(T13,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V13">
         <f>Settings!$B$2*C13/100</f>
         <v/>
       </c>
       <c r="W13">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V13,Settings!$B$5),V13),IF(Settings!$B$9,MROUND(V13,Settings!$B$5),V13))</f>
+        <f>IF(Settings!$B$9,FLOOR(V13,Settings!$B$5),V13)</f>
         <v/>
       </c>
       <c r="X13">
@@ -3190,7 +4218,7 @@
         <v/>
       </c>
       <c r="Y13">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X13,Settings!$B$5),X13),IF(Settings!$B$9,MROUND(X13,Settings!$B$5),X13))</f>
+        <f>IF(Settings!$B$9,CEILING(X13,Settings!$B$5),X13)</f>
         <v/>
       </c>
       <c r="Z13">
@@ -3202,11 +4230,11 @@
         <v/>
       </c>
       <c r="AB13">
-        <f>IF(T13="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA13-Z13)&gt;1E-9),"FIXED",IF(ABS(S13)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T13,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA13-Z13)&gt;1E-9),"FIXED",IF(ABS(S13)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>IF(AB13="FIXED","Close adjusted by SAFE mode",IF(AB13="SAFE","Balance preserved",IF(AB13="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB13="FIXED","Close adjusted by SAFE mode",IF(AB13="SAFE","BUY/SELL balance preserved",IF(AB13="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -3290,12 +4318,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C14&lt;0,E14&lt;0,J14&lt;0,AND(LEN(L14)&gt;0,L14&lt;0)),"ERROR: Negative input",IF(C14&lt;E14,"ERROR: Big BUY must be &gt;= Small SELL",IF(AND(LEN(L14)&gt;0,L14&gt;G14),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N14&lt;0,Q14&lt;0,R14&lt;0),"ERROR: Negative totals",IF(Q14&gt;R14,"ERROR: Rounding broke protection balance",IF(S14&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U14">
+        <f>IF(LEFT(T14,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V14">
         <f>Settings!$B$2*C14/100</f>
         <v/>
       </c>
       <c r="W14">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V14,Settings!$B$5),V14),IF(Settings!$B$9,MROUND(V14,Settings!$B$5),V14))</f>
+        <f>IF(Settings!$B$9,FLOOR(V14,Settings!$B$5),V14)</f>
         <v/>
       </c>
       <c r="X14">
@@ -3303,7 +4335,7 @@
         <v/>
       </c>
       <c r="Y14">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X14,Settings!$B$5),X14),IF(Settings!$B$9,MROUND(X14,Settings!$B$5),X14))</f>
+        <f>IF(Settings!$B$9,CEILING(X14,Settings!$B$5),X14)</f>
         <v/>
       </c>
       <c r="Z14">
@@ -3315,11 +4347,11 @@
         <v/>
       </c>
       <c r="AB14">
-        <f>IF(T14="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA14-Z14)&gt;1E-9),"FIXED",IF(ABS(S14)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T14,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA14-Z14)&gt;1E-9),"FIXED",IF(ABS(S14)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>IF(AB14="FIXED","Close adjusted by SAFE mode",IF(AB14="SAFE","Balance preserved",IF(AB14="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB14="FIXED","Close adjusted by SAFE mode",IF(AB14="SAFE","BUY/SELL balance preserved",IF(AB14="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -3403,12 +4435,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C15&lt;0,E15&lt;0,J15&lt;0,AND(LEN(L15)&gt;0,L15&lt;0)),"ERROR: Negative input",IF(C15&lt;E15,"ERROR: Big BUY must be &gt;= Small SELL",IF(AND(LEN(L15)&gt;0,L15&gt;G15),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N15&lt;0,Q15&lt;0,R15&lt;0),"ERROR: Negative totals",IF(Q15&gt;R15,"ERROR: Rounding broke protection balance",IF(S15&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U15">
+        <f>IF(LEFT(T15,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V15">
         <f>Settings!$B$2*C15/100</f>
         <v/>
       </c>
       <c r="W15">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V15,Settings!$B$5),V15),IF(Settings!$B$9,MROUND(V15,Settings!$B$5),V15))</f>
+        <f>IF(Settings!$B$9,FLOOR(V15,Settings!$B$5),V15)</f>
         <v/>
       </c>
       <c r="X15">
@@ -3416,7 +4452,7 @@
         <v/>
       </c>
       <c r="Y15">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X15,Settings!$B$5),X15),IF(Settings!$B$9,MROUND(X15,Settings!$B$5),X15))</f>
+        <f>IF(Settings!$B$9,CEILING(X15,Settings!$B$5),X15)</f>
         <v/>
       </c>
       <c r="Z15">
@@ -3428,11 +4464,11 @@
         <v/>
       </c>
       <c r="AB15">
-        <f>IF(T15="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA15-Z15)&gt;1E-9),"FIXED",IF(ABS(S15)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T15,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA15-Z15)&gt;1E-9),"FIXED",IF(ABS(S15)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>IF(AB15="FIXED","Close adjusted by SAFE mode",IF(AB15="SAFE","Balance preserved",IF(AB15="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB15="FIXED","Close adjusted by SAFE mode",IF(AB15="SAFE","BUY/SELL balance preserved",IF(AB15="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -3516,12 +4552,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C16&lt;0,E16&lt;0,J16&lt;0,AND(LEN(L16)&gt;0,L16&lt;0)),"ERROR: Negative input",IF(C16&lt;E16,"ERROR: Big BUY must be &gt;= Small SELL",IF(AND(LEN(L16)&gt;0,L16&gt;G16),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N16&lt;0,Q16&lt;0,R16&lt;0),"ERROR: Negative totals",IF(Q16&gt;R16,"ERROR: Rounding broke protection balance",IF(S16&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U16">
+        <f>IF(LEFT(T16,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V16">
         <f>Settings!$B$2*C16/100</f>
         <v/>
       </c>
       <c r="W16">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V16,Settings!$B$5),V16),IF(Settings!$B$9,MROUND(V16,Settings!$B$5),V16))</f>
+        <f>IF(Settings!$B$9,FLOOR(V16,Settings!$B$5),V16)</f>
         <v/>
       </c>
       <c r="X16">
@@ -3529,7 +4569,7 @@
         <v/>
       </c>
       <c r="Y16">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X16,Settings!$B$5),X16),IF(Settings!$B$9,MROUND(X16,Settings!$B$5),X16))</f>
+        <f>IF(Settings!$B$9,CEILING(X16,Settings!$B$5),X16)</f>
         <v/>
       </c>
       <c r="Z16">
@@ -3541,11 +4581,11 @@
         <v/>
       </c>
       <c r="AB16">
-        <f>IF(T16="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA16-Z16)&gt;1E-9),"FIXED",IF(ABS(S16)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T16,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA16-Z16)&gt;1E-9),"FIXED",IF(ABS(S16)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>IF(AB16="FIXED","Close adjusted by SAFE mode",IF(AB16="SAFE","Balance preserved",IF(AB16="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB16="FIXED","Close adjusted by SAFE mode",IF(AB16="SAFE","BUY/SELL balance preserved",IF(AB16="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -3629,12 +4669,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C17&lt;0,E17&lt;0,J17&lt;0,AND(LEN(L17)&gt;0,L17&lt;0)),"ERROR: Negative input",IF(C17&lt;E17,"ERROR: Big BUY must be &gt;= Small SELL",IF(AND(LEN(L17)&gt;0,L17&gt;G17),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N17&lt;0,Q17&lt;0,R17&lt;0),"ERROR: Negative totals",IF(Q17&gt;R17,"ERROR: Rounding broke protection balance",IF(S17&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U17">
+        <f>IF(LEFT(T17,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V17">
         <f>Settings!$B$2*C17/100</f>
         <v/>
       </c>
       <c r="W17">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V17,Settings!$B$5),V17),IF(Settings!$B$9,MROUND(V17,Settings!$B$5),V17))</f>
+        <f>IF(Settings!$B$9,FLOOR(V17,Settings!$B$5),V17)</f>
         <v/>
       </c>
       <c r="X17">
@@ -3642,7 +4686,7 @@
         <v/>
       </c>
       <c r="Y17">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X17,Settings!$B$5),X17),IF(Settings!$B$9,MROUND(X17,Settings!$B$5),X17))</f>
+        <f>IF(Settings!$B$9,CEILING(X17,Settings!$B$5),X17)</f>
         <v/>
       </c>
       <c r="Z17">
@@ -3654,11 +4698,11 @@
         <v/>
       </c>
       <c r="AB17">
-        <f>IF(T17="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA17-Z17)&gt;1E-9),"FIXED",IF(ABS(S17)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T17,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA17-Z17)&gt;1E-9),"FIXED",IF(ABS(S17)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>IF(AB17="FIXED","Close adjusted by SAFE mode",IF(AB17="SAFE","Balance preserved",IF(AB17="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB17="FIXED","Close adjusted by SAFE mode",IF(AB17="SAFE","BUY/SELL balance preserved",IF(AB17="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -3742,12 +4786,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C18&lt;0,E18&lt;0,J18&lt;0,AND(LEN(L18)&gt;0,L18&lt;0)),"ERROR: Negative input",IF(C18&lt;E18,"ERROR: Big BUY must be &gt;= Small SELL",IF(AND(LEN(L18)&gt;0,L18&gt;G18),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N18&lt;0,Q18&lt;0,R18&lt;0),"ERROR: Negative totals",IF(Q18&gt;R18,"ERROR: Rounding broke protection balance",IF(S18&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U18">
+        <f>IF(LEFT(T18,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V18">
         <f>Settings!$B$2*C18/100</f>
         <v/>
       </c>
       <c r="W18">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V18,Settings!$B$5),V18),IF(Settings!$B$9,MROUND(V18,Settings!$B$5),V18))</f>
+        <f>IF(Settings!$B$9,FLOOR(V18,Settings!$B$5),V18)</f>
         <v/>
       </c>
       <c r="X18">
@@ -3755,7 +4803,7 @@
         <v/>
       </c>
       <c r="Y18">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X18,Settings!$B$5),X18),IF(Settings!$B$9,MROUND(X18,Settings!$B$5),X18))</f>
+        <f>IF(Settings!$B$9,CEILING(X18,Settings!$B$5),X18)</f>
         <v/>
       </c>
       <c r="Z18">
@@ -3767,11 +4815,11 @@
         <v/>
       </c>
       <c r="AB18">
-        <f>IF(T18="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA18-Z18)&gt;1E-9),"FIXED",IF(ABS(S18)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T18,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA18-Z18)&gt;1E-9),"FIXED",IF(ABS(S18)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>IF(AB18="FIXED","Close adjusted by SAFE mode",IF(AB18="SAFE","Balance preserved",IF(AB18="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB18="FIXED","Close adjusted by SAFE mode",IF(AB18="SAFE","BUY/SELL balance preserved",IF(AB18="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -3855,12 +4903,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C19&lt;0,E19&lt;0,J19&lt;0,AND(LEN(L19)&gt;0,L19&lt;0)),"ERROR: Negative input",IF(C19&lt;E19,"ERROR: Big BUY must be &gt;= Small SELL",IF(AND(LEN(L19)&gt;0,L19&gt;G19),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N19&lt;0,Q19&lt;0,R19&lt;0),"ERROR: Negative totals",IF(Q19&gt;R19,"ERROR: Rounding broke protection balance",IF(S19&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U19">
+        <f>IF(LEFT(T19,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V19">
         <f>Settings!$B$2*C19/100</f>
         <v/>
       </c>
       <c r="W19">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V19,Settings!$B$5),V19),IF(Settings!$B$9,MROUND(V19,Settings!$B$5),V19))</f>
+        <f>IF(Settings!$B$9,FLOOR(V19,Settings!$B$5),V19)</f>
         <v/>
       </c>
       <c r="X19">
@@ -3868,7 +4920,7 @@
         <v/>
       </c>
       <c r="Y19">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X19,Settings!$B$5),X19),IF(Settings!$B$9,MROUND(X19,Settings!$B$5),X19))</f>
+        <f>IF(Settings!$B$9,CEILING(X19,Settings!$B$5),X19)</f>
         <v/>
       </c>
       <c r="Z19">
@@ -3880,11 +4932,11 @@
         <v/>
       </c>
       <c r="AB19">
-        <f>IF(T19="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA19-Z19)&gt;1E-9),"FIXED",IF(ABS(S19)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T19,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA19-Z19)&gt;1E-9),"FIXED",IF(ABS(S19)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>IF(AB19="FIXED","Close adjusted by SAFE mode",IF(AB19="SAFE","Balance preserved",IF(AB19="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB19="FIXED","Close adjusted by SAFE mode",IF(AB19="SAFE","BUY/SELL balance preserved",IF(AB19="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -3968,12 +5020,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C20&lt;0,E20&lt;0,J20&lt;0,AND(LEN(L20)&gt;0,L20&lt;0)),"ERROR: Negative input",IF(C20&lt;E20,"ERROR: Big BUY must be &gt;= Small SELL",IF(AND(LEN(L20)&gt;0,L20&gt;G20),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N20&lt;0,Q20&lt;0,R20&lt;0),"ERROR: Negative totals",IF(Q20&gt;R20,"ERROR: Rounding broke protection balance",IF(S20&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U20">
+        <f>IF(LEFT(T20,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V20">
         <f>Settings!$B$2*C20/100</f>
         <v/>
       </c>
       <c r="W20">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V20,Settings!$B$5),V20),IF(Settings!$B$9,MROUND(V20,Settings!$B$5),V20))</f>
+        <f>IF(Settings!$B$9,FLOOR(V20,Settings!$B$5),V20)</f>
         <v/>
       </c>
       <c r="X20">
@@ -3981,7 +5037,7 @@
         <v/>
       </c>
       <c r="Y20">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X20,Settings!$B$5),X20),IF(Settings!$B$9,MROUND(X20,Settings!$B$5),X20))</f>
+        <f>IF(Settings!$B$9,CEILING(X20,Settings!$B$5),X20)</f>
         <v/>
       </c>
       <c r="Z20">
@@ -3993,11 +5049,11 @@
         <v/>
       </c>
       <c r="AB20">
-        <f>IF(T20="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA20-Z20)&gt;1E-9),"FIXED",IF(ABS(S20)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T20,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA20-Z20)&gt;1E-9),"FIXED",IF(ABS(S20)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>IF(AB20="FIXED","Close adjusted by SAFE mode",IF(AB20="SAFE","Balance preserved",IF(AB20="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB20="FIXED","Close adjusted by SAFE mode",IF(AB20="SAFE","BUY/SELL balance preserved",IF(AB20="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -4081,12 +5137,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C21&lt;0,E21&lt;0,J21&lt;0,AND(LEN(L21)&gt;0,L21&lt;0)),"ERROR: Negative input",IF(C21&lt;E21,"ERROR: Big BUY must be &gt;= Small SELL",IF(AND(LEN(L21)&gt;0,L21&gt;G21),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N21&lt;0,Q21&lt;0,R21&lt;0),"ERROR: Negative totals",IF(Q21&gt;R21,"ERROR: Rounding broke protection balance",IF(S21&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U21">
+        <f>IF(LEFT(T21,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V21">
         <f>Settings!$B$2*C21/100</f>
         <v/>
       </c>
       <c r="W21">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V21,Settings!$B$5),V21),IF(Settings!$B$9,MROUND(V21,Settings!$B$5),V21))</f>
+        <f>IF(Settings!$B$9,FLOOR(V21,Settings!$B$5),V21)</f>
         <v/>
       </c>
       <c r="X21">
@@ -4094,7 +5154,7 @@
         <v/>
       </c>
       <c r="Y21">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X21,Settings!$B$5),X21),IF(Settings!$B$9,MROUND(X21,Settings!$B$5),X21))</f>
+        <f>IF(Settings!$B$9,CEILING(X21,Settings!$B$5),X21)</f>
         <v/>
       </c>
       <c r="Z21">
@@ -4106,11 +5166,11 @@
         <v/>
       </c>
       <c r="AB21">
-        <f>IF(T21="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA21-Z21)&gt;1E-9),"FIXED",IF(ABS(S21)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T21,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA21-Z21)&gt;1E-9),"FIXED",IF(ABS(S21)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>IF(AB21="FIXED","Close adjusted by SAFE mode",IF(AB21="SAFE","Balance preserved",IF(AB21="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB21="FIXED","Close adjusted by SAFE mode",IF(AB21="SAFE","BUY/SELL balance preserved",IF(AB21="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -4194,12 +5254,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C22&lt;0,E22&lt;0,J22&lt;0,AND(LEN(L22)&gt;0,L22&lt;0)),"ERROR: Negative input",IF(C22&lt;E22,"ERROR: Big BUY must be &gt;= Small SELL",IF(AND(LEN(L22)&gt;0,L22&gt;G22),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N22&lt;0,Q22&lt;0,R22&lt;0),"ERROR: Negative totals",IF(Q22&gt;R22,"ERROR: Rounding broke protection balance",IF(S22&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U22">
+        <f>IF(LEFT(T22,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V22">
         <f>Settings!$B$2*C22/100</f>
         <v/>
       </c>
       <c r="W22">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V22,Settings!$B$5),V22),IF(Settings!$B$9,MROUND(V22,Settings!$B$5),V22))</f>
+        <f>IF(Settings!$B$9,FLOOR(V22,Settings!$B$5),V22)</f>
         <v/>
       </c>
       <c r="X22">
@@ -4207,7 +5271,7 @@
         <v/>
       </c>
       <c r="Y22">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X22,Settings!$B$5),X22),IF(Settings!$B$9,MROUND(X22,Settings!$B$5),X22))</f>
+        <f>IF(Settings!$B$9,CEILING(X22,Settings!$B$5),X22)</f>
         <v/>
       </c>
       <c r="Z22">
@@ -4219,11 +5283,11 @@
         <v/>
       </c>
       <c r="AB22">
-        <f>IF(T22="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA22-Z22)&gt;1E-9),"FIXED",IF(ABS(S22)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T22,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA22-Z22)&gt;1E-9),"FIXED",IF(ABS(S22)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>IF(AB22="FIXED","Close adjusted by SAFE mode",IF(AB22="SAFE","Balance preserved",IF(AB22="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB22="FIXED","Close adjusted by SAFE mode",IF(AB22="SAFE","BUY/SELL balance preserved",IF(AB22="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -4307,12 +5371,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C23&lt;0,E23&lt;0,J23&lt;0,AND(LEN(L23)&gt;0,L23&lt;0)),"ERROR: Negative input",IF(C23&lt;E23,"ERROR: Big BUY must be &gt;= Small SELL",IF(AND(LEN(L23)&gt;0,L23&gt;G23),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N23&lt;0,Q23&lt;0,R23&lt;0),"ERROR: Negative totals",IF(Q23&gt;R23,"ERROR: Rounding broke protection balance",IF(S23&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U23">
+        <f>IF(LEFT(T23,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V23">
         <f>Settings!$B$2*C23/100</f>
         <v/>
       </c>
       <c r="W23">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V23,Settings!$B$5),V23),IF(Settings!$B$9,MROUND(V23,Settings!$B$5),V23))</f>
+        <f>IF(Settings!$B$9,FLOOR(V23,Settings!$B$5),V23)</f>
         <v/>
       </c>
       <c r="X23">
@@ -4320,7 +5388,7 @@
         <v/>
       </c>
       <c r="Y23">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X23,Settings!$B$5),X23),IF(Settings!$B$9,MROUND(X23,Settings!$B$5),X23))</f>
+        <f>IF(Settings!$B$9,CEILING(X23,Settings!$B$5),X23)</f>
         <v/>
       </c>
       <c r="Z23">
@@ -4332,11 +5400,11 @@
         <v/>
       </c>
       <c r="AB23">
-        <f>IF(T23="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA23-Z23)&gt;1E-9),"FIXED",IF(ABS(S23)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T23,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA23-Z23)&gt;1E-9),"FIXED",IF(ABS(S23)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>IF(AB23="FIXED","Close adjusted by SAFE mode",IF(AB23="SAFE","Balance preserved",IF(AB23="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB23="FIXED","Close adjusted by SAFE mode",IF(AB23="SAFE","BUY/SELL balance preserved",IF(AB23="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -4420,12 +5488,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C24&lt;0,E24&lt;0,J24&lt;0,AND(LEN(L24)&gt;0,L24&lt;0)),"ERROR: Negative input",IF(C24&lt;E24,"ERROR: Big BUY must be &gt;= Small SELL",IF(AND(LEN(L24)&gt;0,L24&gt;G24),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N24&lt;0,Q24&lt;0,R24&lt;0),"ERROR: Negative totals",IF(Q24&gt;R24,"ERROR: Rounding broke protection balance",IF(S24&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U24">
+        <f>IF(LEFT(T24,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V24">
         <f>Settings!$B$2*C24/100</f>
         <v/>
       </c>
       <c r="W24">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V24,Settings!$B$5),V24),IF(Settings!$B$9,MROUND(V24,Settings!$B$5),V24))</f>
+        <f>IF(Settings!$B$9,FLOOR(V24,Settings!$B$5),V24)</f>
         <v/>
       </c>
       <c r="X24">
@@ -4433,7 +5505,7 @@
         <v/>
       </c>
       <c r="Y24">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X24,Settings!$B$5),X24),IF(Settings!$B$9,MROUND(X24,Settings!$B$5),X24))</f>
+        <f>IF(Settings!$B$9,CEILING(X24,Settings!$B$5),X24)</f>
         <v/>
       </c>
       <c r="Z24">
@@ -4445,11 +5517,11 @@
         <v/>
       </c>
       <c r="AB24">
-        <f>IF(T24="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA24-Z24)&gt;1E-9),"FIXED",IF(ABS(S24)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T24,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA24-Z24)&gt;1E-9),"FIXED",IF(ABS(S24)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>IF(AB24="FIXED","Close adjusted by SAFE mode",IF(AB24="SAFE","Balance preserved",IF(AB24="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB24="FIXED","Close adjusted by SAFE mode",IF(AB24="SAFE","BUY/SELL balance preserved",IF(AB24="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -4533,12 +5605,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C25&lt;0,E25&lt;0,J25&lt;0,AND(LEN(L25)&gt;0,L25&lt;0)),"ERROR: Negative input",IF(C25&lt;E25,"ERROR: Big BUY must be &gt;= Small SELL",IF(AND(LEN(L25)&gt;0,L25&gt;G25),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N25&lt;0,Q25&lt;0,R25&lt;0),"ERROR: Negative totals",IF(Q25&gt;R25,"ERROR: Rounding broke protection balance",IF(S25&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U25">
+        <f>IF(LEFT(T25,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V25">
         <f>Settings!$B$2*C25/100</f>
         <v/>
       </c>
       <c r="W25">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V25,Settings!$B$5),V25),IF(Settings!$B$9,MROUND(V25,Settings!$B$5),V25))</f>
+        <f>IF(Settings!$B$9,FLOOR(V25,Settings!$B$5),V25)</f>
         <v/>
       </c>
       <c r="X25">
@@ -4546,7 +5622,7 @@
         <v/>
       </c>
       <c r="Y25">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X25,Settings!$B$5),X25),IF(Settings!$B$9,MROUND(X25,Settings!$B$5),X25))</f>
+        <f>IF(Settings!$B$9,CEILING(X25,Settings!$B$5),X25)</f>
         <v/>
       </c>
       <c r="Z25">
@@ -4558,11 +5634,11 @@
         <v/>
       </c>
       <c r="AB25">
-        <f>IF(T25="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA25-Z25)&gt;1E-9),"FIXED",IF(ABS(S25)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T25,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA25-Z25)&gt;1E-9),"FIXED",IF(ABS(S25)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>IF(AB25="FIXED","Close adjusted by SAFE mode",IF(AB25="SAFE","Balance preserved",IF(AB25="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB25="FIXED","Close adjusted by SAFE mode",IF(AB25="SAFE","BUY/SELL balance preserved",IF(AB25="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -4646,12 +5722,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C26&lt;0,E26&lt;0,J26&lt;0,AND(LEN(L26)&gt;0,L26&lt;0)),"ERROR: Negative input",IF(C26&lt;E26,"ERROR: Big BUY must be &gt;= Small SELL",IF(AND(LEN(L26)&gt;0,L26&gt;G26),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N26&lt;0,Q26&lt;0,R26&lt;0),"ERROR: Negative totals",IF(Q26&gt;R26,"ERROR: Rounding broke protection balance",IF(S26&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U26">
+        <f>IF(LEFT(T26,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V26">
         <f>Settings!$B$2*C26/100</f>
         <v/>
       </c>
       <c r="W26">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V26,Settings!$B$5),V26),IF(Settings!$B$9,MROUND(V26,Settings!$B$5),V26))</f>
+        <f>IF(Settings!$B$9,FLOOR(V26,Settings!$B$5),V26)</f>
         <v/>
       </c>
       <c r="X26">
@@ -4659,7 +5739,7 @@
         <v/>
       </c>
       <c r="Y26">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X26,Settings!$B$5),X26),IF(Settings!$B$9,MROUND(X26,Settings!$B$5),X26))</f>
+        <f>IF(Settings!$B$9,CEILING(X26,Settings!$B$5),X26)</f>
         <v/>
       </c>
       <c r="Z26">
@@ -4671,11 +5751,11 @@
         <v/>
       </c>
       <c r="AB26">
-        <f>IF(T26="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA26-Z26)&gt;1E-9),"FIXED",IF(ABS(S26)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T26,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA26-Z26)&gt;1E-9),"FIXED",IF(ABS(S26)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>IF(AB26="FIXED","Close adjusted by SAFE mode",IF(AB26="SAFE","Balance preserved",IF(AB26="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB26="FIXED","Close adjusted by SAFE mode",IF(AB26="SAFE","BUY/SELL balance preserved",IF(AB26="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -4759,12 +5839,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C27&lt;0,E27&lt;0,J27&lt;0,AND(LEN(L27)&gt;0,L27&lt;0)),"ERROR: Negative input",IF(C27&lt;E27,"ERROR: Big BUY must be &gt;= Small SELL",IF(AND(LEN(L27)&gt;0,L27&gt;G27),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N27&lt;0,Q27&lt;0,R27&lt;0),"ERROR: Negative totals",IF(Q27&gt;R27,"ERROR: Rounding broke protection balance",IF(S27&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U27">
+        <f>IF(LEFT(T27,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V27">
         <f>Settings!$B$2*C27/100</f>
         <v/>
       </c>
       <c r="W27">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V27,Settings!$B$5),V27),IF(Settings!$B$9,MROUND(V27,Settings!$B$5),V27))</f>
+        <f>IF(Settings!$B$9,FLOOR(V27,Settings!$B$5),V27)</f>
         <v/>
       </c>
       <c r="X27">
@@ -4772,7 +5856,7 @@
         <v/>
       </c>
       <c r="Y27">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X27,Settings!$B$5),X27),IF(Settings!$B$9,MROUND(X27,Settings!$B$5),X27))</f>
+        <f>IF(Settings!$B$9,CEILING(X27,Settings!$B$5),X27)</f>
         <v/>
       </c>
       <c r="Z27">
@@ -4784,11 +5868,11 @@
         <v/>
       </c>
       <c r="AB27">
-        <f>IF(T27="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA27-Z27)&gt;1E-9),"FIXED",IF(ABS(S27)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T27,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA27-Z27)&gt;1E-9),"FIXED",IF(ABS(S27)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>IF(AB27="FIXED","Close adjusted by SAFE mode",IF(AB27="SAFE","Balance preserved",IF(AB27="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB27="FIXED","Close adjusted by SAFE mode",IF(AB27="SAFE","BUY/SELL balance preserved",IF(AB27="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -4872,12 +5956,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C28&lt;0,E28&lt;0,J28&lt;0,AND(LEN(L28)&gt;0,L28&lt;0)),"ERROR: Negative input",IF(C28&lt;E28,"ERROR: Big BUY must be &gt;= Small SELL",IF(AND(LEN(L28)&gt;0,L28&gt;G28),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N28&lt;0,Q28&lt;0,R28&lt;0),"ERROR: Negative totals",IF(Q28&gt;R28,"ERROR: Rounding broke protection balance",IF(S28&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U28">
+        <f>IF(LEFT(T28,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V28">
         <f>Settings!$B$2*C28/100</f>
         <v/>
       </c>
       <c r="W28">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V28,Settings!$B$5),V28),IF(Settings!$B$9,MROUND(V28,Settings!$B$5),V28))</f>
+        <f>IF(Settings!$B$9,FLOOR(V28,Settings!$B$5),V28)</f>
         <v/>
       </c>
       <c r="X28">
@@ -4885,7 +5973,7 @@
         <v/>
       </c>
       <c r="Y28">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X28,Settings!$B$5),X28),IF(Settings!$B$9,MROUND(X28,Settings!$B$5),X28))</f>
+        <f>IF(Settings!$B$9,CEILING(X28,Settings!$B$5),X28)</f>
         <v/>
       </c>
       <c r="Z28">
@@ -4897,11 +5985,11 @@
         <v/>
       </c>
       <c r="AB28">
-        <f>IF(T28="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA28-Z28)&gt;1E-9),"FIXED",IF(ABS(S28)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T28,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA28-Z28)&gt;1E-9),"FIXED",IF(ABS(S28)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>IF(AB28="FIXED","Close adjusted by SAFE mode",IF(AB28="SAFE","Balance preserved",IF(AB28="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB28="FIXED","Close adjusted by SAFE mode",IF(AB28="SAFE","BUY/SELL balance preserved",IF(AB28="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -4985,12 +6073,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C29&lt;0,E29&lt;0,J29&lt;0,AND(LEN(L29)&gt;0,L29&lt;0)),"ERROR: Negative input",IF(C29&lt;E29,"ERROR: Big BUY must be &gt;= Small SELL",IF(AND(LEN(L29)&gt;0,L29&gt;G29),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N29&lt;0,Q29&lt;0,R29&lt;0),"ERROR: Negative totals",IF(Q29&gt;R29,"ERROR: Rounding broke protection balance",IF(S29&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U29">
+        <f>IF(LEFT(T29,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V29">
         <f>Settings!$B$2*C29/100</f>
         <v/>
       </c>
       <c r="W29">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V29,Settings!$B$5),V29),IF(Settings!$B$9,MROUND(V29,Settings!$B$5),V29))</f>
+        <f>IF(Settings!$B$9,FLOOR(V29,Settings!$B$5),V29)</f>
         <v/>
       </c>
       <c r="X29">
@@ -4998,7 +6090,7 @@
         <v/>
       </c>
       <c r="Y29">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X29,Settings!$B$5),X29),IF(Settings!$B$9,MROUND(X29,Settings!$B$5),X29))</f>
+        <f>IF(Settings!$B$9,CEILING(X29,Settings!$B$5),X29)</f>
         <v/>
       </c>
       <c r="Z29">
@@ -5010,11 +6102,11 @@
         <v/>
       </c>
       <c r="AB29">
-        <f>IF(T29="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA29-Z29)&gt;1E-9),"FIXED",IF(ABS(S29)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T29,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA29-Z29)&gt;1E-9),"FIXED",IF(ABS(S29)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>IF(AB29="FIXED","Close adjusted by SAFE mode",IF(AB29="SAFE","Balance preserved",IF(AB29="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB29="FIXED","Close adjusted by SAFE mode",IF(AB29="SAFE","BUY/SELL balance preserved",IF(AB29="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -5098,12 +6190,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C30&lt;0,E30&lt;0,J30&lt;0,AND(LEN(L30)&gt;0,L30&lt;0)),"ERROR: Negative input",IF(C30&lt;E30,"ERROR: Big BUY must be &gt;= Small SELL",IF(AND(LEN(L30)&gt;0,L30&gt;G30),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N30&lt;0,Q30&lt;0,R30&lt;0),"ERROR: Negative totals",IF(Q30&gt;R30,"ERROR: Rounding broke protection balance",IF(S30&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U30">
+        <f>IF(LEFT(T30,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V30">
         <f>Settings!$B$2*C30/100</f>
         <v/>
       </c>
       <c r="W30">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V30,Settings!$B$5),V30),IF(Settings!$B$9,MROUND(V30,Settings!$B$5),V30))</f>
+        <f>IF(Settings!$B$9,FLOOR(V30,Settings!$B$5),V30)</f>
         <v/>
       </c>
       <c r="X30">
@@ -5111,7 +6207,7 @@
         <v/>
       </c>
       <c r="Y30">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X30,Settings!$B$5),X30),IF(Settings!$B$9,MROUND(X30,Settings!$B$5),X30))</f>
+        <f>IF(Settings!$B$9,CEILING(X30,Settings!$B$5),X30)</f>
         <v/>
       </c>
       <c r="Z30">
@@ -5123,11 +6219,11 @@
         <v/>
       </c>
       <c r="AB30">
-        <f>IF(T30="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA30-Z30)&gt;1E-9),"FIXED",IF(ABS(S30)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T30,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA30-Z30)&gt;1E-9),"FIXED",IF(ABS(S30)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>IF(AB30="FIXED","Close adjusted by SAFE mode",IF(AB30="SAFE","Balance preserved",IF(AB30="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB30="FIXED","Close adjusted by SAFE mode",IF(AB30="SAFE","BUY/SELL balance preserved",IF(AB30="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -5211,12 +6307,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C31&lt;0,E31&lt;0,J31&lt;0,AND(LEN(L31)&gt;0,L31&lt;0)),"ERROR: Negative input",IF(C31&lt;E31,"ERROR: Big BUY must be &gt;= Small SELL",IF(AND(LEN(L31)&gt;0,L31&gt;G31),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N31&lt;0,Q31&lt;0,R31&lt;0),"ERROR: Negative totals",IF(Q31&gt;R31,"ERROR: Rounding broke protection balance",IF(S31&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U31">
+        <f>IF(LEFT(T31,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V31">
         <f>Settings!$B$2*C31/100</f>
         <v/>
       </c>
       <c r="W31">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V31,Settings!$B$5),V31),IF(Settings!$B$9,MROUND(V31,Settings!$B$5),V31))</f>
+        <f>IF(Settings!$B$9,FLOOR(V31,Settings!$B$5),V31)</f>
         <v/>
       </c>
       <c r="X31">
@@ -5224,7 +6324,7 @@
         <v/>
       </c>
       <c r="Y31">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X31,Settings!$B$5),X31),IF(Settings!$B$9,MROUND(X31,Settings!$B$5),X31))</f>
+        <f>IF(Settings!$B$9,CEILING(X31,Settings!$B$5),X31)</f>
         <v/>
       </c>
       <c r="Z31">
@@ -5236,11 +6336,11 @@
         <v/>
       </c>
       <c r="AB31">
-        <f>IF(T31="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA31-Z31)&gt;1E-9),"FIXED",IF(ABS(S31)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T31,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA31-Z31)&gt;1E-9),"FIXED",IF(ABS(S31)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>IF(AB31="FIXED","Close adjusted by SAFE mode",IF(AB31="SAFE","Balance preserved",IF(AB31="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB31="FIXED","Close adjusted by SAFE mode",IF(AB31="SAFE","BUY/SELL balance preserved",IF(AB31="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -5324,12 +6424,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C32&lt;0,E32&lt;0,J32&lt;0,AND(LEN(L32)&gt;0,L32&lt;0)),"ERROR: Negative input",IF(C32&lt;E32,"ERROR: Big BUY must be &gt;= Small SELL",IF(AND(LEN(L32)&gt;0,L32&gt;G32),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N32&lt;0,Q32&lt;0,R32&lt;0),"ERROR: Negative totals",IF(Q32&gt;R32,"ERROR: Rounding broke protection balance",IF(S32&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U32">
+        <f>IF(LEFT(T32,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V32">
         <f>Settings!$B$2*C32/100</f>
         <v/>
       </c>
       <c r="W32">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V32,Settings!$B$5),V32),IF(Settings!$B$9,MROUND(V32,Settings!$B$5),V32))</f>
+        <f>IF(Settings!$B$9,FLOOR(V32,Settings!$B$5),V32)</f>
         <v/>
       </c>
       <c r="X32">
@@ -5337,7 +6441,7 @@
         <v/>
       </c>
       <c r="Y32">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X32,Settings!$B$5),X32),IF(Settings!$B$9,MROUND(X32,Settings!$B$5),X32))</f>
+        <f>IF(Settings!$B$9,CEILING(X32,Settings!$B$5),X32)</f>
         <v/>
       </c>
       <c r="Z32">
@@ -5349,11 +6453,11 @@
         <v/>
       </c>
       <c r="AB32">
-        <f>IF(T32="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA32-Z32)&gt;1E-9),"FIXED",IF(ABS(S32)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T32,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA32-Z32)&gt;1E-9),"FIXED",IF(ABS(S32)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>IF(AB32="FIXED","Close adjusted by SAFE mode",IF(AB32="SAFE","Balance preserved",IF(AB32="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB32="FIXED","Close adjusted by SAFE mode",IF(AB32="SAFE","BUY/SELL balance preserved",IF(AB32="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -5437,12 +6541,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C33&lt;0,E33&lt;0,J33&lt;0,AND(LEN(L33)&gt;0,L33&lt;0)),"ERROR: Negative input",IF(C33&lt;E33,"ERROR: Big BUY must be &gt;= Small SELL",IF(AND(LEN(L33)&gt;0,L33&gt;G33),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N33&lt;0,Q33&lt;0,R33&lt;0),"ERROR: Negative totals",IF(Q33&gt;R33,"ERROR: Rounding broke protection balance",IF(S33&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U33">
+        <f>IF(LEFT(T33,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V33">
         <f>Settings!$B$2*C33/100</f>
         <v/>
       </c>
       <c r="W33">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V33,Settings!$B$5),V33),IF(Settings!$B$9,MROUND(V33,Settings!$B$5),V33))</f>
+        <f>IF(Settings!$B$9,FLOOR(V33,Settings!$B$5),V33)</f>
         <v/>
       </c>
       <c r="X33">
@@ -5450,7 +6558,7 @@
         <v/>
       </c>
       <c r="Y33">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X33,Settings!$B$5),X33),IF(Settings!$B$9,MROUND(X33,Settings!$B$5),X33))</f>
+        <f>IF(Settings!$B$9,CEILING(X33,Settings!$B$5),X33)</f>
         <v/>
       </c>
       <c r="Z33">
@@ -5462,11 +6570,11 @@
         <v/>
       </c>
       <c r="AB33">
-        <f>IF(T33="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA33-Z33)&gt;1E-9),"FIXED",IF(ABS(S33)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T33,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA33-Z33)&gt;1E-9),"FIXED",IF(ABS(S33)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>IF(AB33="FIXED","Close adjusted by SAFE mode",IF(AB33="SAFE","Balance preserved",IF(AB33="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB33="FIXED","Close adjusted by SAFE mode",IF(AB33="SAFE","BUY/SELL balance preserved",IF(AB33="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -5550,12 +6658,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C34&lt;0,E34&lt;0,J34&lt;0,AND(LEN(L34)&gt;0,L34&lt;0)),"ERROR: Negative input",IF(C34&lt;E34,"ERROR: Big BUY must be &gt;= Small SELL",IF(AND(LEN(L34)&gt;0,L34&gt;G34),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N34&lt;0,Q34&lt;0,R34&lt;0),"ERROR: Negative totals",IF(Q34&gt;R34,"ERROR: Rounding broke protection balance",IF(S34&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U34">
+        <f>IF(LEFT(T34,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V34">
         <f>Settings!$B$2*C34/100</f>
         <v/>
       </c>
       <c r="W34">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V34,Settings!$B$5),V34),IF(Settings!$B$9,MROUND(V34,Settings!$B$5),V34))</f>
+        <f>IF(Settings!$B$9,FLOOR(V34,Settings!$B$5),V34)</f>
         <v/>
       </c>
       <c r="X34">
@@ -5563,7 +6675,7 @@
         <v/>
       </c>
       <c r="Y34">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X34,Settings!$B$5),X34),IF(Settings!$B$9,MROUND(X34,Settings!$B$5),X34))</f>
+        <f>IF(Settings!$B$9,CEILING(X34,Settings!$B$5),X34)</f>
         <v/>
       </c>
       <c r="Z34">
@@ -5575,11 +6687,11 @@
         <v/>
       </c>
       <c r="AB34">
-        <f>IF(T34="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA34-Z34)&gt;1E-9),"FIXED",IF(ABS(S34)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T34,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA34-Z34)&gt;1E-9),"FIXED",IF(ABS(S34)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>IF(AB34="FIXED","Close adjusted by SAFE mode",IF(AB34="SAFE","Balance preserved",IF(AB34="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB34="FIXED","Close adjusted by SAFE mode",IF(AB34="SAFE","BUY/SELL balance preserved",IF(AB34="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -5663,12 +6775,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C35&lt;0,E35&lt;0,J35&lt;0,AND(LEN(L35)&gt;0,L35&lt;0)),"ERROR: Negative input",IF(C35&lt;E35,"ERROR: Big BUY must be &gt;= Small SELL",IF(AND(LEN(L35)&gt;0,L35&gt;G35),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N35&lt;0,Q35&lt;0,R35&lt;0),"ERROR: Negative totals",IF(Q35&gt;R35,"ERROR: Rounding broke protection balance",IF(S35&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U35">
+        <f>IF(LEFT(T35,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V35">
         <f>Settings!$B$2*C35/100</f>
         <v/>
       </c>
       <c r="W35">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V35,Settings!$B$5),V35),IF(Settings!$B$9,MROUND(V35,Settings!$B$5),V35))</f>
+        <f>IF(Settings!$B$9,FLOOR(V35,Settings!$B$5),V35)</f>
         <v/>
       </c>
       <c r="X35">
@@ -5676,7 +6792,7 @@
         <v/>
       </c>
       <c r="Y35">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X35,Settings!$B$5),X35),IF(Settings!$B$9,MROUND(X35,Settings!$B$5),X35))</f>
+        <f>IF(Settings!$B$9,CEILING(X35,Settings!$B$5),X35)</f>
         <v/>
       </c>
       <c r="Z35">
@@ -5688,11 +6804,11 @@
         <v/>
       </c>
       <c r="AB35">
-        <f>IF(T35="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA35-Z35)&gt;1E-9),"FIXED",IF(ABS(S35)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T35,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA35-Z35)&gt;1E-9),"FIXED",IF(ABS(S35)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>IF(AB35="FIXED","Close adjusted by SAFE mode",IF(AB35="SAFE","Balance preserved",IF(AB35="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB35="FIXED","Close adjusted by SAFE mode",IF(AB35="SAFE","BUY/SELL balance preserved",IF(AB35="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -5776,12 +6892,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C36&lt;0,E36&lt;0,J36&lt;0,AND(LEN(L36)&gt;0,L36&lt;0)),"ERROR: Negative input",IF(C36&lt;E36,"ERROR: Big BUY must be &gt;= Small SELL",IF(AND(LEN(L36)&gt;0,L36&gt;G36),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N36&lt;0,Q36&lt;0,R36&lt;0),"ERROR: Negative totals",IF(Q36&gt;R36,"ERROR: Rounding broke protection balance",IF(S36&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U36">
+        <f>IF(LEFT(T36,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V36">
         <f>Settings!$B$2*C36/100</f>
         <v/>
       </c>
       <c r="W36">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V36,Settings!$B$5),V36),IF(Settings!$B$9,MROUND(V36,Settings!$B$5),V36))</f>
+        <f>IF(Settings!$B$9,FLOOR(V36,Settings!$B$5),V36)</f>
         <v/>
       </c>
       <c r="X36">
@@ -5789,7 +6909,7 @@
         <v/>
       </c>
       <c r="Y36">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X36,Settings!$B$5),X36),IF(Settings!$B$9,MROUND(X36,Settings!$B$5),X36))</f>
+        <f>IF(Settings!$B$9,CEILING(X36,Settings!$B$5),X36)</f>
         <v/>
       </c>
       <c r="Z36">
@@ -5801,11 +6921,11 @@
         <v/>
       </c>
       <c r="AB36">
-        <f>IF(T36="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA36-Z36)&gt;1E-9),"FIXED",IF(ABS(S36)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T36,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA36-Z36)&gt;1E-9),"FIXED",IF(ABS(S36)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>IF(AB36="FIXED","Close adjusted by SAFE mode",IF(AB36="SAFE","Balance preserved",IF(AB36="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB36="FIXED","Close adjusted by SAFE mode",IF(AB36="SAFE","BUY/SELL balance preserved",IF(AB36="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -5889,12 +7009,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C37&lt;0,E37&lt;0,J37&lt;0,AND(LEN(L37)&gt;0,L37&lt;0)),"ERROR: Negative input",IF(C37&lt;E37,"ERROR: Big BUY must be &gt;= Small SELL",IF(AND(LEN(L37)&gt;0,L37&gt;G37),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N37&lt;0,Q37&lt;0,R37&lt;0),"ERROR: Negative totals",IF(Q37&gt;R37,"ERROR: Rounding broke protection balance",IF(S37&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U37">
+        <f>IF(LEFT(T37,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V37">
         <f>Settings!$B$2*C37/100</f>
         <v/>
       </c>
       <c r="W37">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V37,Settings!$B$5),V37),IF(Settings!$B$9,MROUND(V37,Settings!$B$5),V37))</f>
+        <f>IF(Settings!$B$9,FLOOR(V37,Settings!$B$5),V37)</f>
         <v/>
       </c>
       <c r="X37">
@@ -5902,7 +7026,7 @@
         <v/>
       </c>
       <c r="Y37">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X37,Settings!$B$5),X37),IF(Settings!$B$9,MROUND(X37,Settings!$B$5),X37))</f>
+        <f>IF(Settings!$B$9,CEILING(X37,Settings!$B$5),X37)</f>
         <v/>
       </c>
       <c r="Z37">
@@ -5914,11 +7038,11 @@
         <v/>
       </c>
       <c r="AB37">
-        <f>IF(T37="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA37-Z37)&gt;1E-9),"FIXED",IF(ABS(S37)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T37,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA37-Z37)&gt;1E-9),"FIXED",IF(ABS(S37)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>IF(AB37="FIXED","Close adjusted by SAFE mode",IF(AB37="SAFE","Balance preserved",IF(AB37="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB37="FIXED","Close adjusted by SAFE mode",IF(AB37="SAFE","BUY/SELL balance preserved",IF(AB37="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -6002,12 +7126,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C38&lt;0,E38&lt;0,J38&lt;0,AND(LEN(L38)&gt;0,L38&lt;0)),"ERROR: Negative input",IF(C38&lt;E38,"ERROR: Big BUY must be &gt;= Small SELL",IF(AND(LEN(L38)&gt;0,L38&gt;G38),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N38&lt;0,Q38&lt;0,R38&lt;0),"ERROR: Negative totals",IF(Q38&gt;R38,"ERROR: Rounding broke protection balance",IF(S38&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U38">
+        <f>IF(LEFT(T38,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V38">
         <f>Settings!$B$2*C38/100</f>
         <v/>
       </c>
       <c r="W38">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V38,Settings!$B$5),V38),IF(Settings!$B$9,MROUND(V38,Settings!$B$5),V38))</f>
+        <f>IF(Settings!$B$9,FLOOR(V38,Settings!$B$5),V38)</f>
         <v/>
       </c>
       <c r="X38">
@@ -6015,7 +7143,7 @@
         <v/>
       </c>
       <c r="Y38">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X38,Settings!$B$5),X38),IF(Settings!$B$9,MROUND(X38,Settings!$B$5),X38))</f>
+        <f>IF(Settings!$B$9,CEILING(X38,Settings!$B$5),X38)</f>
         <v/>
       </c>
       <c r="Z38">
@@ -6027,11 +7155,11 @@
         <v/>
       </c>
       <c r="AB38">
-        <f>IF(T38="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA38-Z38)&gt;1E-9),"FIXED",IF(ABS(S38)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T38,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA38-Z38)&gt;1E-9),"FIXED",IF(ABS(S38)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>IF(AB38="FIXED","Close adjusted by SAFE mode",IF(AB38="SAFE","Balance preserved",IF(AB38="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB38="FIXED","Close adjusted by SAFE mode",IF(AB38="SAFE","BUY/SELL balance preserved",IF(AB38="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -6115,12 +7243,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C39&lt;0,E39&lt;0,J39&lt;0,AND(LEN(L39)&gt;0,L39&lt;0)),"ERROR: Negative input",IF(C39&lt;E39,"ERROR: Big BUY must be &gt;= Small SELL",IF(AND(LEN(L39)&gt;0,L39&gt;G39),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N39&lt;0,Q39&lt;0,R39&lt;0),"ERROR: Negative totals",IF(Q39&gt;R39,"ERROR: Rounding broke protection balance",IF(S39&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U39">
+        <f>IF(LEFT(T39,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V39">
         <f>Settings!$B$2*C39/100</f>
         <v/>
       </c>
       <c r="W39">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V39,Settings!$B$5),V39),IF(Settings!$B$9,MROUND(V39,Settings!$B$5),V39))</f>
+        <f>IF(Settings!$B$9,FLOOR(V39,Settings!$B$5),V39)</f>
         <v/>
       </c>
       <c r="X39">
@@ -6128,7 +7260,7 @@
         <v/>
       </c>
       <c r="Y39">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X39,Settings!$B$5),X39),IF(Settings!$B$9,MROUND(X39,Settings!$B$5),X39))</f>
+        <f>IF(Settings!$B$9,CEILING(X39,Settings!$B$5),X39)</f>
         <v/>
       </c>
       <c r="Z39">
@@ -6140,11 +7272,11 @@
         <v/>
       </c>
       <c r="AB39">
-        <f>IF(T39="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA39-Z39)&gt;1E-9),"FIXED",IF(ABS(S39)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T39,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA39-Z39)&gt;1E-9),"FIXED",IF(ABS(S39)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>IF(AB39="FIXED","Close adjusted by SAFE mode",IF(AB39="SAFE","Balance preserved",IF(AB39="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB39="FIXED","Close adjusted by SAFE mode",IF(AB39="SAFE","BUY/SELL balance preserved",IF(AB39="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -6228,12 +7360,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C40&lt;0,E40&lt;0,J40&lt;0,AND(LEN(L40)&gt;0,L40&lt;0)),"ERROR: Negative input",IF(C40&lt;E40,"ERROR: Big BUY must be &gt;= Small SELL",IF(AND(LEN(L40)&gt;0,L40&gt;G40),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N40&lt;0,Q40&lt;0,R40&lt;0),"ERROR: Negative totals",IF(Q40&gt;R40,"ERROR: Rounding broke protection balance",IF(S40&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U40">
+        <f>IF(LEFT(T40,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V40">
         <f>Settings!$B$2*C40/100</f>
         <v/>
       </c>
       <c r="W40">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V40,Settings!$B$5),V40),IF(Settings!$B$9,MROUND(V40,Settings!$B$5),V40))</f>
+        <f>IF(Settings!$B$9,FLOOR(V40,Settings!$B$5),V40)</f>
         <v/>
       </c>
       <c r="X40">
@@ -6241,7 +7377,7 @@
         <v/>
       </c>
       <c r="Y40">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X40,Settings!$B$5),X40),IF(Settings!$B$9,MROUND(X40,Settings!$B$5),X40))</f>
+        <f>IF(Settings!$B$9,CEILING(X40,Settings!$B$5),X40)</f>
         <v/>
       </c>
       <c r="Z40">
@@ -6253,11 +7389,11 @@
         <v/>
       </c>
       <c r="AB40">
-        <f>IF(T40="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA40-Z40)&gt;1E-9),"FIXED",IF(ABS(S40)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T40,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA40-Z40)&gt;1E-9),"FIXED",IF(ABS(S40)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>IF(AB40="FIXED","Close adjusted by SAFE mode",IF(AB40="SAFE","Balance preserved",IF(AB40="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB40="FIXED","Close adjusted by SAFE mode",IF(AB40="SAFE","BUY/SELL balance preserved",IF(AB40="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -6341,12 +7477,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C41&lt;0,E41&lt;0,J41&lt;0,AND(LEN(L41)&gt;0,L41&lt;0)),"ERROR: Negative input",IF(C41&lt;E41,"ERROR: Big BUY must be &gt;= Small SELL",IF(AND(LEN(L41)&gt;0,L41&gt;G41),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N41&lt;0,Q41&lt;0,R41&lt;0),"ERROR: Negative totals",IF(Q41&gt;R41,"ERROR: Rounding broke protection balance",IF(S41&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U41">
+        <f>IF(LEFT(T41,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V41">
         <f>Settings!$B$2*C41/100</f>
         <v/>
       </c>
       <c r="W41">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V41,Settings!$B$5),V41),IF(Settings!$B$9,MROUND(V41,Settings!$B$5),V41))</f>
+        <f>IF(Settings!$B$9,FLOOR(V41,Settings!$B$5),V41)</f>
         <v/>
       </c>
       <c r="X41">
@@ -6354,7 +7494,7 @@
         <v/>
       </c>
       <c r="Y41">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X41,Settings!$B$5),X41),IF(Settings!$B$9,MROUND(X41,Settings!$B$5),X41))</f>
+        <f>IF(Settings!$B$9,CEILING(X41,Settings!$B$5),X41)</f>
         <v/>
       </c>
       <c r="Z41">
@@ -6366,11 +7506,11 @@
         <v/>
       </c>
       <c r="AB41">
-        <f>IF(T41="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA41-Z41)&gt;1E-9),"FIXED",IF(ABS(S41)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T41,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA41-Z41)&gt;1E-9),"FIXED",IF(ABS(S41)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>IF(AB41="FIXED","Close adjusted by SAFE mode",IF(AB41="SAFE","Balance preserved",IF(AB41="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB41="FIXED","Close adjusted by SAFE mode",IF(AB41="SAFE","BUY/SELL balance preserved",IF(AB41="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -6415,7 +7555,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Big SELL %</t>
+          <t>Big %</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -6425,7 +7565,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Small BUY %</t>
+          <t>Small %</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -6490,7 +7630,7 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Total Opp %</t>
+          <t>Total Opposite %</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
@@ -6614,6 +7754,10 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C2&lt;0,E2&lt;0,J2&lt;0,AND(LEN(L2)&gt;0,L2&lt;0)),"ERROR: Negative input",IF(C2&lt;E2,"ERROR: Big SELL must be &gt;= Small BUY",IF(AND(LEN(L2)&gt;0,L2&gt;G2),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N2&lt;0,Q2&lt;0,R2&lt;0),"ERROR: Negative totals",IF(Q2&gt;R2,"ERROR: Rounding broke protection balance",IF(S2&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U2">
+        <f>IF(LEFT(T2,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
@@ -6633,11 +7777,11 @@
         <v>0</v>
       </c>
       <c r="AB2">
-        <f>IF(T2="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA2-Z2)&gt;1E-9),"FIXED",IF(ABS(S2)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T2,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA2-Z2)&gt;1E-9),"FIXED",IF(ABS(S2)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>IF(AB2="FIXED","Close adjusted by SAFE mode",IF(AB2="SAFE","Balance preserved",IF(AB2="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB2="FIXED","Close adjusted by SAFE mode",IF(AB2="SAFE","BUY/SELL balance preserved",IF(AB2="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -6720,12 +7864,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C3&lt;0,E3&lt;0,J3&lt;0,AND(LEN(L3)&gt;0,L3&lt;0)),"ERROR: Negative input",IF(C3&lt;E3,"ERROR: Big SELL must be &gt;= Small BUY",IF(AND(LEN(L3)&gt;0,L3&gt;G3),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N3&lt;0,Q3&lt;0,R3&lt;0),"ERROR: Negative totals",IF(Q3&gt;R3,"ERROR: Rounding broke protection balance",IF(S3&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U3">
+        <f>IF(LEFT(T3,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V3">
         <f>Settings!$B$2*C3/100</f>
         <v/>
       </c>
       <c r="W3">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V3,Settings!$B$5),V3),IF(Settings!$B$9,MROUND(V3,Settings!$B$5),V3))</f>
+        <f>IF(Settings!$B$9,FLOOR(V3,Settings!$B$5),V3)</f>
         <v/>
       </c>
       <c r="X3">
@@ -6733,7 +7881,7 @@
         <v/>
       </c>
       <c r="Y3">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X3,Settings!$B$5),X3),IF(Settings!$B$9,MROUND(X3,Settings!$B$5),X3))</f>
+        <f>IF(Settings!$B$9,CEILING(X3,Settings!$B$5),X3)</f>
         <v/>
       </c>
       <c r="Z3">
@@ -6745,11 +7893,11 @@
         <v/>
       </c>
       <c r="AB3">
-        <f>IF(T3="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA3-Z3)&gt;1E-9),"FIXED",IF(ABS(S3)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T3,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA3-Z3)&gt;1E-9),"FIXED",IF(ABS(S3)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>IF(AB3="FIXED","Close adjusted by SAFE mode",IF(AB3="SAFE","Balance preserved",IF(AB3="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB3="FIXED","Close adjusted by SAFE mode",IF(AB3="SAFE","BUY/SELL balance preserved",IF(AB3="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -6833,12 +7981,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C4&lt;0,E4&lt;0,J4&lt;0,AND(LEN(L4)&gt;0,L4&lt;0)),"ERROR: Negative input",IF(C4&lt;E4,"ERROR: Big SELL must be &gt;= Small BUY",IF(AND(LEN(L4)&gt;0,L4&gt;G4),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N4&lt;0,Q4&lt;0,R4&lt;0),"ERROR: Negative totals",IF(Q4&gt;R4,"ERROR: Rounding broke protection balance",IF(S4&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U4">
+        <f>IF(LEFT(T4,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V4">
         <f>Settings!$B$2*C4/100</f>
         <v/>
       </c>
       <c r="W4">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V4,Settings!$B$5),V4),IF(Settings!$B$9,MROUND(V4,Settings!$B$5),V4))</f>
+        <f>IF(Settings!$B$9,FLOOR(V4,Settings!$B$5),V4)</f>
         <v/>
       </c>
       <c r="X4">
@@ -6846,7 +7998,7 @@
         <v/>
       </c>
       <c r="Y4">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X4,Settings!$B$5),X4),IF(Settings!$B$9,MROUND(X4,Settings!$B$5),X4))</f>
+        <f>IF(Settings!$B$9,CEILING(X4,Settings!$B$5),X4)</f>
         <v/>
       </c>
       <c r="Z4">
@@ -6858,11 +8010,11 @@
         <v/>
       </c>
       <c r="AB4">
-        <f>IF(T4="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA4-Z4)&gt;1E-9),"FIXED",IF(ABS(S4)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T4,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA4-Z4)&gt;1E-9),"FIXED",IF(ABS(S4)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>IF(AB4="FIXED","Close adjusted by SAFE mode",IF(AB4="SAFE","Balance preserved",IF(AB4="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB4="FIXED","Close adjusted by SAFE mode",IF(AB4="SAFE","BUY/SELL balance preserved",IF(AB4="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -6946,12 +8098,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C5&lt;0,E5&lt;0,J5&lt;0,AND(LEN(L5)&gt;0,L5&lt;0)),"ERROR: Negative input",IF(C5&lt;E5,"ERROR: Big SELL must be &gt;= Small BUY",IF(AND(LEN(L5)&gt;0,L5&gt;G5),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N5&lt;0,Q5&lt;0,R5&lt;0),"ERROR: Negative totals",IF(Q5&gt;R5,"ERROR: Rounding broke protection balance",IF(S5&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U5">
+        <f>IF(LEFT(T5,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V5">
         <f>Settings!$B$2*C5/100</f>
         <v/>
       </c>
       <c r="W5">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V5,Settings!$B$5),V5),IF(Settings!$B$9,MROUND(V5,Settings!$B$5),V5))</f>
+        <f>IF(Settings!$B$9,FLOOR(V5,Settings!$B$5),V5)</f>
         <v/>
       </c>
       <c r="X5">
@@ -6959,7 +8115,7 @@
         <v/>
       </c>
       <c r="Y5">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X5,Settings!$B$5),X5),IF(Settings!$B$9,MROUND(X5,Settings!$B$5),X5))</f>
+        <f>IF(Settings!$B$9,CEILING(X5,Settings!$B$5),X5)</f>
         <v/>
       </c>
       <c r="Z5">
@@ -6971,11 +8127,11 @@
         <v/>
       </c>
       <c r="AB5">
-        <f>IF(T5="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA5-Z5)&gt;1E-9),"FIXED",IF(ABS(S5)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T5,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA5-Z5)&gt;1E-9),"FIXED",IF(ABS(S5)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>IF(AB5="FIXED","Close adjusted by SAFE mode",IF(AB5="SAFE","Balance preserved",IF(AB5="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB5="FIXED","Close adjusted by SAFE mode",IF(AB5="SAFE","BUY/SELL balance preserved",IF(AB5="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -7059,12 +8215,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C6&lt;0,E6&lt;0,J6&lt;0,AND(LEN(L6)&gt;0,L6&lt;0)),"ERROR: Negative input",IF(C6&lt;E6,"ERROR: Big SELL must be &gt;= Small BUY",IF(AND(LEN(L6)&gt;0,L6&gt;G6),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N6&lt;0,Q6&lt;0,R6&lt;0),"ERROR: Negative totals",IF(Q6&gt;R6,"ERROR: Rounding broke protection balance",IF(S6&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U6">
+        <f>IF(LEFT(T6,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V6">
         <f>Settings!$B$2*C6/100</f>
         <v/>
       </c>
       <c r="W6">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V6,Settings!$B$5),V6),IF(Settings!$B$9,MROUND(V6,Settings!$B$5),V6))</f>
+        <f>IF(Settings!$B$9,FLOOR(V6,Settings!$B$5),V6)</f>
         <v/>
       </c>
       <c r="X6">
@@ -7072,7 +8232,7 @@
         <v/>
       </c>
       <c r="Y6">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X6,Settings!$B$5),X6),IF(Settings!$B$9,MROUND(X6,Settings!$B$5),X6))</f>
+        <f>IF(Settings!$B$9,CEILING(X6,Settings!$B$5),X6)</f>
         <v/>
       </c>
       <c r="Z6">
@@ -7084,11 +8244,11 @@
         <v/>
       </c>
       <c r="AB6">
-        <f>IF(T6="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA6-Z6)&gt;1E-9),"FIXED",IF(ABS(S6)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T6,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA6-Z6)&gt;1E-9),"FIXED",IF(ABS(S6)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>IF(AB6="FIXED","Close adjusted by SAFE mode",IF(AB6="SAFE","Balance preserved",IF(AB6="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB6="FIXED","Close adjusted by SAFE mode",IF(AB6="SAFE","BUY/SELL balance preserved",IF(AB6="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -7172,12 +8332,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C7&lt;0,E7&lt;0,J7&lt;0,AND(LEN(L7)&gt;0,L7&lt;0)),"ERROR: Negative input",IF(C7&lt;E7,"ERROR: Big SELL must be &gt;= Small BUY",IF(AND(LEN(L7)&gt;0,L7&gt;G7),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N7&lt;0,Q7&lt;0,R7&lt;0),"ERROR: Negative totals",IF(Q7&gt;R7,"ERROR: Rounding broke protection balance",IF(S7&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U7">
+        <f>IF(LEFT(T7,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V7">
         <f>Settings!$B$2*C7/100</f>
         <v/>
       </c>
       <c r="W7">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V7,Settings!$B$5),V7),IF(Settings!$B$9,MROUND(V7,Settings!$B$5),V7))</f>
+        <f>IF(Settings!$B$9,FLOOR(V7,Settings!$B$5),V7)</f>
         <v/>
       </c>
       <c r="X7">
@@ -7185,7 +8349,7 @@
         <v/>
       </c>
       <c r="Y7">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X7,Settings!$B$5),X7),IF(Settings!$B$9,MROUND(X7,Settings!$B$5),X7))</f>
+        <f>IF(Settings!$B$9,CEILING(X7,Settings!$B$5),X7)</f>
         <v/>
       </c>
       <c r="Z7">
@@ -7197,11 +8361,11 @@
         <v/>
       </c>
       <c r="AB7">
-        <f>IF(T7="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA7-Z7)&gt;1E-9),"FIXED",IF(ABS(S7)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T7,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA7-Z7)&gt;1E-9),"FIXED",IF(ABS(S7)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>IF(AB7="FIXED","Close adjusted by SAFE mode",IF(AB7="SAFE","Balance preserved",IF(AB7="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB7="FIXED","Close adjusted by SAFE mode",IF(AB7="SAFE","BUY/SELL balance preserved",IF(AB7="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -7285,12 +8449,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C8&lt;0,E8&lt;0,J8&lt;0,AND(LEN(L8)&gt;0,L8&lt;0)),"ERROR: Negative input",IF(C8&lt;E8,"ERROR: Big SELL must be &gt;= Small BUY",IF(AND(LEN(L8)&gt;0,L8&gt;G8),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N8&lt;0,Q8&lt;0,R8&lt;0),"ERROR: Negative totals",IF(Q8&gt;R8,"ERROR: Rounding broke protection balance",IF(S8&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U8">
+        <f>IF(LEFT(T8,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V8">
         <f>Settings!$B$2*C8/100</f>
         <v/>
       </c>
       <c r="W8">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V8,Settings!$B$5),V8),IF(Settings!$B$9,MROUND(V8,Settings!$B$5),V8))</f>
+        <f>IF(Settings!$B$9,FLOOR(V8,Settings!$B$5),V8)</f>
         <v/>
       </c>
       <c r="X8">
@@ -7298,7 +8466,7 @@
         <v/>
       </c>
       <c r="Y8">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X8,Settings!$B$5),X8),IF(Settings!$B$9,MROUND(X8,Settings!$B$5),X8))</f>
+        <f>IF(Settings!$B$9,CEILING(X8,Settings!$B$5),X8)</f>
         <v/>
       </c>
       <c r="Z8">
@@ -7310,11 +8478,11 @@
         <v/>
       </c>
       <c r="AB8">
-        <f>IF(T8="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA8-Z8)&gt;1E-9),"FIXED",IF(ABS(S8)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T8,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA8-Z8)&gt;1E-9),"FIXED",IF(ABS(S8)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>IF(AB8="FIXED","Close adjusted by SAFE mode",IF(AB8="SAFE","Balance preserved",IF(AB8="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB8="FIXED","Close adjusted by SAFE mode",IF(AB8="SAFE","BUY/SELL balance preserved",IF(AB8="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -7398,12 +8566,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C9&lt;0,E9&lt;0,J9&lt;0,AND(LEN(L9)&gt;0,L9&lt;0)),"ERROR: Negative input",IF(C9&lt;E9,"ERROR: Big SELL must be &gt;= Small BUY",IF(AND(LEN(L9)&gt;0,L9&gt;G9),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N9&lt;0,Q9&lt;0,R9&lt;0),"ERROR: Negative totals",IF(Q9&gt;R9,"ERROR: Rounding broke protection balance",IF(S9&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U9">
+        <f>IF(LEFT(T9,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V9">
         <f>Settings!$B$2*C9/100</f>
         <v/>
       </c>
       <c r="W9">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V9,Settings!$B$5),V9),IF(Settings!$B$9,MROUND(V9,Settings!$B$5),V9))</f>
+        <f>IF(Settings!$B$9,FLOOR(V9,Settings!$B$5),V9)</f>
         <v/>
       </c>
       <c r="X9">
@@ -7411,7 +8583,7 @@
         <v/>
       </c>
       <c r="Y9">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X9,Settings!$B$5),X9),IF(Settings!$B$9,MROUND(X9,Settings!$B$5),X9))</f>
+        <f>IF(Settings!$B$9,CEILING(X9,Settings!$B$5),X9)</f>
         <v/>
       </c>
       <c r="Z9">
@@ -7423,11 +8595,11 @@
         <v/>
       </c>
       <c r="AB9">
-        <f>IF(T9="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA9-Z9)&gt;1E-9),"FIXED",IF(ABS(S9)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T9,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA9-Z9)&gt;1E-9),"FIXED",IF(ABS(S9)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>IF(AB9="FIXED","Close adjusted by SAFE mode",IF(AB9="SAFE","Balance preserved",IF(AB9="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB9="FIXED","Close adjusted by SAFE mode",IF(AB9="SAFE","BUY/SELL balance preserved",IF(AB9="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -7511,12 +8683,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C10&lt;0,E10&lt;0,J10&lt;0,AND(LEN(L10)&gt;0,L10&lt;0)),"ERROR: Negative input",IF(C10&lt;E10,"ERROR: Big SELL must be &gt;= Small BUY",IF(AND(LEN(L10)&gt;0,L10&gt;G10),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N10&lt;0,Q10&lt;0,R10&lt;0),"ERROR: Negative totals",IF(Q10&gt;R10,"ERROR: Rounding broke protection balance",IF(S10&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U10">
+        <f>IF(LEFT(T10,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V10">
         <f>Settings!$B$2*C10/100</f>
         <v/>
       </c>
       <c r="W10">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V10,Settings!$B$5),V10),IF(Settings!$B$9,MROUND(V10,Settings!$B$5),V10))</f>
+        <f>IF(Settings!$B$9,FLOOR(V10,Settings!$B$5),V10)</f>
         <v/>
       </c>
       <c r="X10">
@@ -7524,7 +8700,7 @@
         <v/>
       </c>
       <c r="Y10">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X10,Settings!$B$5),X10),IF(Settings!$B$9,MROUND(X10,Settings!$B$5),X10))</f>
+        <f>IF(Settings!$B$9,CEILING(X10,Settings!$B$5),X10)</f>
         <v/>
       </c>
       <c r="Z10">
@@ -7536,11 +8712,11 @@
         <v/>
       </c>
       <c r="AB10">
-        <f>IF(T10="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA10-Z10)&gt;1E-9),"FIXED",IF(ABS(S10)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T10,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA10-Z10)&gt;1E-9),"FIXED",IF(ABS(S10)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>IF(AB10="FIXED","Close adjusted by SAFE mode",IF(AB10="SAFE","Balance preserved",IF(AB10="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB10="FIXED","Close adjusted by SAFE mode",IF(AB10="SAFE","BUY/SELL balance preserved",IF(AB10="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -7624,12 +8800,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C11&lt;0,E11&lt;0,J11&lt;0,AND(LEN(L11)&gt;0,L11&lt;0)),"ERROR: Negative input",IF(C11&lt;E11,"ERROR: Big SELL must be &gt;= Small BUY",IF(AND(LEN(L11)&gt;0,L11&gt;G11),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N11&lt;0,Q11&lt;0,R11&lt;0),"ERROR: Negative totals",IF(Q11&gt;R11,"ERROR: Rounding broke protection balance",IF(S11&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U11">
+        <f>IF(LEFT(T11,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V11">
         <f>Settings!$B$2*C11/100</f>
         <v/>
       </c>
       <c r="W11">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V11,Settings!$B$5),V11),IF(Settings!$B$9,MROUND(V11,Settings!$B$5),V11))</f>
+        <f>IF(Settings!$B$9,FLOOR(V11,Settings!$B$5),V11)</f>
         <v/>
       </c>
       <c r="X11">
@@ -7637,7 +8817,7 @@
         <v/>
       </c>
       <c r="Y11">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X11,Settings!$B$5),X11),IF(Settings!$B$9,MROUND(X11,Settings!$B$5),X11))</f>
+        <f>IF(Settings!$B$9,CEILING(X11,Settings!$B$5),X11)</f>
         <v/>
       </c>
       <c r="Z11">
@@ -7649,11 +8829,11 @@
         <v/>
       </c>
       <c r="AB11">
-        <f>IF(T11="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA11-Z11)&gt;1E-9),"FIXED",IF(ABS(S11)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T11,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA11-Z11)&gt;1E-9),"FIXED",IF(ABS(S11)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>IF(AB11="FIXED","Close adjusted by SAFE mode",IF(AB11="SAFE","Balance preserved",IF(AB11="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB11="FIXED","Close adjusted by SAFE mode",IF(AB11="SAFE","BUY/SELL balance preserved",IF(AB11="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -7737,12 +8917,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C12&lt;0,E12&lt;0,J12&lt;0,AND(LEN(L12)&gt;0,L12&lt;0)),"ERROR: Negative input",IF(C12&lt;E12,"ERROR: Big SELL must be &gt;= Small BUY",IF(AND(LEN(L12)&gt;0,L12&gt;G12),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N12&lt;0,Q12&lt;0,R12&lt;0),"ERROR: Negative totals",IF(Q12&gt;R12,"ERROR: Rounding broke protection balance",IF(S12&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U12">
+        <f>IF(LEFT(T12,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V12">
         <f>Settings!$B$2*C12/100</f>
         <v/>
       </c>
       <c r="W12">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V12,Settings!$B$5),V12),IF(Settings!$B$9,MROUND(V12,Settings!$B$5),V12))</f>
+        <f>IF(Settings!$B$9,FLOOR(V12,Settings!$B$5),V12)</f>
         <v/>
       </c>
       <c r="X12">
@@ -7750,7 +8934,7 @@
         <v/>
       </c>
       <c r="Y12">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X12,Settings!$B$5),X12),IF(Settings!$B$9,MROUND(X12,Settings!$B$5),X12))</f>
+        <f>IF(Settings!$B$9,CEILING(X12,Settings!$B$5),X12)</f>
         <v/>
       </c>
       <c r="Z12">
@@ -7762,11 +8946,11 @@
         <v/>
       </c>
       <c r="AB12">
-        <f>IF(T12="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA12-Z12)&gt;1E-9),"FIXED",IF(ABS(S12)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T12,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA12-Z12)&gt;1E-9),"FIXED",IF(ABS(S12)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>IF(AB12="FIXED","Close adjusted by SAFE mode",IF(AB12="SAFE","Balance preserved",IF(AB12="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB12="FIXED","Close adjusted by SAFE mode",IF(AB12="SAFE","BUY/SELL balance preserved",IF(AB12="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -7850,12 +9034,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C13&lt;0,E13&lt;0,J13&lt;0,AND(LEN(L13)&gt;0,L13&lt;0)),"ERROR: Negative input",IF(C13&lt;E13,"ERROR: Big SELL must be &gt;= Small BUY",IF(AND(LEN(L13)&gt;0,L13&gt;G13),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N13&lt;0,Q13&lt;0,R13&lt;0),"ERROR: Negative totals",IF(Q13&gt;R13,"ERROR: Rounding broke protection balance",IF(S13&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U13">
+        <f>IF(LEFT(T13,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V13">
         <f>Settings!$B$2*C13/100</f>
         <v/>
       </c>
       <c r="W13">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V13,Settings!$B$5),V13),IF(Settings!$B$9,MROUND(V13,Settings!$B$5),V13))</f>
+        <f>IF(Settings!$B$9,FLOOR(V13,Settings!$B$5),V13)</f>
         <v/>
       </c>
       <c r="X13">
@@ -7863,7 +9051,7 @@
         <v/>
       </c>
       <c r="Y13">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X13,Settings!$B$5),X13),IF(Settings!$B$9,MROUND(X13,Settings!$B$5),X13))</f>
+        <f>IF(Settings!$B$9,CEILING(X13,Settings!$B$5),X13)</f>
         <v/>
       </c>
       <c r="Z13">
@@ -7875,11 +9063,11 @@
         <v/>
       </c>
       <c r="AB13">
-        <f>IF(T13="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA13-Z13)&gt;1E-9),"FIXED",IF(ABS(S13)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T13,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA13-Z13)&gt;1E-9),"FIXED",IF(ABS(S13)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>IF(AB13="FIXED","Close adjusted by SAFE mode",IF(AB13="SAFE","Balance preserved",IF(AB13="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB13="FIXED","Close adjusted by SAFE mode",IF(AB13="SAFE","BUY/SELL balance preserved",IF(AB13="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -7963,12 +9151,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C14&lt;0,E14&lt;0,J14&lt;0,AND(LEN(L14)&gt;0,L14&lt;0)),"ERROR: Negative input",IF(C14&lt;E14,"ERROR: Big SELL must be &gt;= Small BUY",IF(AND(LEN(L14)&gt;0,L14&gt;G14),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N14&lt;0,Q14&lt;0,R14&lt;0),"ERROR: Negative totals",IF(Q14&gt;R14,"ERROR: Rounding broke protection balance",IF(S14&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U14">
+        <f>IF(LEFT(T14,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V14">
         <f>Settings!$B$2*C14/100</f>
         <v/>
       </c>
       <c r="W14">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V14,Settings!$B$5),V14),IF(Settings!$B$9,MROUND(V14,Settings!$B$5),V14))</f>
+        <f>IF(Settings!$B$9,FLOOR(V14,Settings!$B$5),V14)</f>
         <v/>
       </c>
       <c r="X14">
@@ -7976,7 +9168,7 @@
         <v/>
       </c>
       <c r="Y14">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X14,Settings!$B$5),X14),IF(Settings!$B$9,MROUND(X14,Settings!$B$5),X14))</f>
+        <f>IF(Settings!$B$9,CEILING(X14,Settings!$B$5),X14)</f>
         <v/>
       </c>
       <c r="Z14">
@@ -7988,11 +9180,11 @@
         <v/>
       </c>
       <c r="AB14">
-        <f>IF(T14="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA14-Z14)&gt;1E-9),"FIXED",IF(ABS(S14)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T14,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA14-Z14)&gt;1E-9),"FIXED",IF(ABS(S14)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>IF(AB14="FIXED","Close adjusted by SAFE mode",IF(AB14="SAFE","Balance preserved",IF(AB14="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB14="FIXED","Close adjusted by SAFE mode",IF(AB14="SAFE","BUY/SELL balance preserved",IF(AB14="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -8076,12 +9268,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C15&lt;0,E15&lt;0,J15&lt;0,AND(LEN(L15)&gt;0,L15&lt;0)),"ERROR: Negative input",IF(C15&lt;E15,"ERROR: Big SELL must be &gt;= Small BUY",IF(AND(LEN(L15)&gt;0,L15&gt;G15),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N15&lt;0,Q15&lt;0,R15&lt;0),"ERROR: Negative totals",IF(Q15&gt;R15,"ERROR: Rounding broke protection balance",IF(S15&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U15">
+        <f>IF(LEFT(T15,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V15">
         <f>Settings!$B$2*C15/100</f>
         <v/>
       </c>
       <c r="W15">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V15,Settings!$B$5),V15),IF(Settings!$B$9,MROUND(V15,Settings!$B$5),V15))</f>
+        <f>IF(Settings!$B$9,FLOOR(V15,Settings!$B$5),V15)</f>
         <v/>
       </c>
       <c r="X15">
@@ -8089,7 +9285,7 @@
         <v/>
       </c>
       <c r="Y15">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X15,Settings!$B$5),X15),IF(Settings!$B$9,MROUND(X15,Settings!$B$5),X15))</f>
+        <f>IF(Settings!$B$9,CEILING(X15,Settings!$B$5),X15)</f>
         <v/>
       </c>
       <c r="Z15">
@@ -8101,11 +9297,11 @@
         <v/>
       </c>
       <c r="AB15">
-        <f>IF(T15="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA15-Z15)&gt;1E-9),"FIXED",IF(ABS(S15)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T15,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA15-Z15)&gt;1E-9),"FIXED",IF(ABS(S15)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>IF(AB15="FIXED","Close adjusted by SAFE mode",IF(AB15="SAFE","Balance preserved",IF(AB15="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB15="FIXED","Close adjusted by SAFE mode",IF(AB15="SAFE","BUY/SELL balance preserved",IF(AB15="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -8189,12 +9385,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C16&lt;0,E16&lt;0,J16&lt;0,AND(LEN(L16)&gt;0,L16&lt;0)),"ERROR: Negative input",IF(C16&lt;E16,"ERROR: Big SELL must be &gt;= Small BUY",IF(AND(LEN(L16)&gt;0,L16&gt;G16),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N16&lt;0,Q16&lt;0,R16&lt;0),"ERROR: Negative totals",IF(Q16&gt;R16,"ERROR: Rounding broke protection balance",IF(S16&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U16">
+        <f>IF(LEFT(T16,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V16">
         <f>Settings!$B$2*C16/100</f>
         <v/>
       </c>
       <c r="W16">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V16,Settings!$B$5),V16),IF(Settings!$B$9,MROUND(V16,Settings!$B$5),V16))</f>
+        <f>IF(Settings!$B$9,FLOOR(V16,Settings!$B$5),V16)</f>
         <v/>
       </c>
       <c r="X16">
@@ -8202,7 +9402,7 @@
         <v/>
       </c>
       <c r="Y16">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X16,Settings!$B$5),X16),IF(Settings!$B$9,MROUND(X16,Settings!$B$5),X16))</f>
+        <f>IF(Settings!$B$9,CEILING(X16,Settings!$B$5),X16)</f>
         <v/>
       </c>
       <c r="Z16">
@@ -8214,11 +9414,11 @@
         <v/>
       </c>
       <c r="AB16">
-        <f>IF(T16="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA16-Z16)&gt;1E-9),"FIXED",IF(ABS(S16)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T16,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA16-Z16)&gt;1E-9),"FIXED",IF(ABS(S16)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>IF(AB16="FIXED","Close adjusted by SAFE mode",IF(AB16="SAFE","Balance preserved",IF(AB16="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB16="FIXED","Close adjusted by SAFE mode",IF(AB16="SAFE","BUY/SELL balance preserved",IF(AB16="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -8302,12 +9502,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C17&lt;0,E17&lt;0,J17&lt;0,AND(LEN(L17)&gt;0,L17&lt;0)),"ERROR: Negative input",IF(C17&lt;E17,"ERROR: Big SELL must be &gt;= Small BUY",IF(AND(LEN(L17)&gt;0,L17&gt;G17),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N17&lt;0,Q17&lt;0,R17&lt;0),"ERROR: Negative totals",IF(Q17&gt;R17,"ERROR: Rounding broke protection balance",IF(S17&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U17">
+        <f>IF(LEFT(T17,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V17">
         <f>Settings!$B$2*C17/100</f>
         <v/>
       </c>
       <c r="W17">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V17,Settings!$B$5),V17),IF(Settings!$B$9,MROUND(V17,Settings!$B$5),V17))</f>
+        <f>IF(Settings!$B$9,FLOOR(V17,Settings!$B$5),V17)</f>
         <v/>
       </c>
       <c r="X17">
@@ -8315,7 +9519,7 @@
         <v/>
       </c>
       <c r="Y17">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X17,Settings!$B$5),X17),IF(Settings!$B$9,MROUND(X17,Settings!$B$5),X17))</f>
+        <f>IF(Settings!$B$9,CEILING(X17,Settings!$B$5),X17)</f>
         <v/>
       </c>
       <c r="Z17">
@@ -8327,11 +9531,11 @@
         <v/>
       </c>
       <c r="AB17">
-        <f>IF(T17="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA17-Z17)&gt;1E-9),"FIXED",IF(ABS(S17)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T17,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA17-Z17)&gt;1E-9),"FIXED",IF(ABS(S17)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>IF(AB17="FIXED","Close adjusted by SAFE mode",IF(AB17="SAFE","Balance preserved",IF(AB17="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB17="FIXED","Close adjusted by SAFE mode",IF(AB17="SAFE","BUY/SELL balance preserved",IF(AB17="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -8415,12 +9619,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C18&lt;0,E18&lt;0,J18&lt;0,AND(LEN(L18)&gt;0,L18&lt;0)),"ERROR: Negative input",IF(C18&lt;E18,"ERROR: Big SELL must be &gt;= Small BUY",IF(AND(LEN(L18)&gt;0,L18&gt;G18),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N18&lt;0,Q18&lt;0,R18&lt;0),"ERROR: Negative totals",IF(Q18&gt;R18,"ERROR: Rounding broke protection balance",IF(S18&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U18">
+        <f>IF(LEFT(T18,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V18">
         <f>Settings!$B$2*C18/100</f>
         <v/>
       </c>
       <c r="W18">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V18,Settings!$B$5),V18),IF(Settings!$B$9,MROUND(V18,Settings!$B$5),V18))</f>
+        <f>IF(Settings!$B$9,FLOOR(V18,Settings!$B$5),V18)</f>
         <v/>
       </c>
       <c r="X18">
@@ -8428,7 +9636,7 @@
         <v/>
       </c>
       <c r="Y18">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X18,Settings!$B$5),X18),IF(Settings!$B$9,MROUND(X18,Settings!$B$5),X18))</f>
+        <f>IF(Settings!$B$9,CEILING(X18,Settings!$B$5),X18)</f>
         <v/>
       </c>
       <c r="Z18">
@@ -8440,11 +9648,11 @@
         <v/>
       </c>
       <c r="AB18">
-        <f>IF(T18="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA18-Z18)&gt;1E-9),"FIXED",IF(ABS(S18)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T18,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA18-Z18)&gt;1E-9),"FIXED",IF(ABS(S18)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>IF(AB18="FIXED","Close adjusted by SAFE mode",IF(AB18="SAFE","Balance preserved",IF(AB18="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB18="FIXED","Close adjusted by SAFE mode",IF(AB18="SAFE","BUY/SELL balance preserved",IF(AB18="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -8528,12 +9736,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C19&lt;0,E19&lt;0,J19&lt;0,AND(LEN(L19)&gt;0,L19&lt;0)),"ERROR: Negative input",IF(C19&lt;E19,"ERROR: Big SELL must be &gt;= Small BUY",IF(AND(LEN(L19)&gt;0,L19&gt;G19),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N19&lt;0,Q19&lt;0,R19&lt;0),"ERROR: Negative totals",IF(Q19&gt;R19,"ERROR: Rounding broke protection balance",IF(S19&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U19">
+        <f>IF(LEFT(T19,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V19">
         <f>Settings!$B$2*C19/100</f>
         <v/>
       </c>
       <c r="W19">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V19,Settings!$B$5),V19),IF(Settings!$B$9,MROUND(V19,Settings!$B$5),V19))</f>
+        <f>IF(Settings!$B$9,FLOOR(V19,Settings!$B$5),V19)</f>
         <v/>
       </c>
       <c r="X19">
@@ -8541,7 +9753,7 @@
         <v/>
       </c>
       <c r="Y19">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X19,Settings!$B$5),X19),IF(Settings!$B$9,MROUND(X19,Settings!$B$5),X19))</f>
+        <f>IF(Settings!$B$9,CEILING(X19,Settings!$B$5),X19)</f>
         <v/>
       </c>
       <c r="Z19">
@@ -8553,11 +9765,11 @@
         <v/>
       </c>
       <c r="AB19">
-        <f>IF(T19="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA19-Z19)&gt;1E-9),"FIXED",IF(ABS(S19)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T19,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA19-Z19)&gt;1E-9),"FIXED",IF(ABS(S19)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>IF(AB19="FIXED","Close adjusted by SAFE mode",IF(AB19="SAFE","Balance preserved",IF(AB19="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB19="FIXED","Close adjusted by SAFE mode",IF(AB19="SAFE","BUY/SELL balance preserved",IF(AB19="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -8641,12 +9853,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C20&lt;0,E20&lt;0,J20&lt;0,AND(LEN(L20)&gt;0,L20&lt;0)),"ERROR: Negative input",IF(C20&lt;E20,"ERROR: Big SELL must be &gt;= Small BUY",IF(AND(LEN(L20)&gt;0,L20&gt;G20),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N20&lt;0,Q20&lt;0,R20&lt;0),"ERROR: Negative totals",IF(Q20&gt;R20,"ERROR: Rounding broke protection balance",IF(S20&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U20">
+        <f>IF(LEFT(T20,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V20">
         <f>Settings!$B$2*C20/100</f>
         <v/>
       </c>
       <c r="W20">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V20,Settings!$B$5),V20),IF(Settings!$B$9,MROUND(V20,Settings!$B$5),V20))</f>
+        <f>IF(Settings!$B$9,FLOOR(V20,Settings!$B$5),V20)</f>
         <v/>
       </c>
       <c r="X20">
@@ -8654,7 +9870,7 @@
         <v/>
       </c>
       <c r="Y20">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X20,Settings!$B$5),X20),IF(Settings!$B$9,MROUND(X20,Settings!$B$5),X20))</f>
+        <f>IF(Settings!$B$9,CEILING(X20,Settings!$B$5),X20)</f>
         <v/>
       </c>
       <c r="Z20">
@@ -8666,11 +9882,11 @@
         <v/>
       </c>
       <c r="AB20">
-        <f>IF(T20="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA20-Z20)&gt;1E-9),"FIXED",IF(ABS(S20)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T20,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA20-Z20)&gt;1E-9),"FIXED",IF(ABS(S20)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>IF(AB20="FIXED","Close adjusted by SAFE mode",IF(AB20="SAFE","Balance preserved",IF(AB20="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB20="FIXED","Close adjusted by SAFE mode",IF(AB20="SAFE","BUY/SELL balance preserved",IF(AB20="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -8754,12 +9970,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C21&lt;0,E21&lt;0,J21&lt;0,AND(LEN(L21)&gt;0,L21&lt;0)),"ERROR: Negative input",IF(C21&lt;E21,"ERROR: Big SELL must be &gt;= Small BUY",IF(AND(LEN(L21)&gt;0,L21&gt;G21),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N21&lt;0,Q21&lt;0,R21&lt;0),"ERROR: Negative totals",IF(Q21&gt;R21,"ERROR: Rounding broke protection balance",IF(S21&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U21">
+        <f>IF(LEFT(T21,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V21">
         <f>Settings!$B$2*C21/100</f>
         <v/>
       </c>
       <c r="W21">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V21,Settings!$B$5),V21),IF(Settings!$B$9,MROUND(V21,Settings!$B$5),V21))</f>
+        <f>IF(Settings!$B$9,FLOOR(V21,Settings!$B$5),V21)</f>
         <v/>
       </c>
       <c r="X21">
@@ -8767,7 +9987,7 @@
         <v/>
       </c>
       <c r="Y21">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X21,Settings!$B$5),X21),IF(Settings!$B$9,MROUND(X21,Settings!$B$5),X21))</f>
+        <f>IF(Settings!$B$9,CEILING(X21,Settings!$B$5),X21)</f>
         <v/>
       </c>
       <c r="Z21">
@@ -8779,11 +9999,11 @@
         <v/>
       </c>
       <c r="AB21">
-        <f>IF(T21="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA21-Z21)&gt;1E-9),"FIXED",IF(ABS(S21)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T21,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA21-Z21)&gt;1E-9),"FIXED",IF(ABS(S21)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>IF(AB21="FIXED","Close adjusted by SAFE mode",IF(AB21="SAFE","Balance preserved",IF(AB21="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB21="FIXED","Close adjusted by SAFE mode",IF(AB21="SAFE","BUY/SELL balance preserved",IF(AB21="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -8867,12 +10087,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C22&lt;0,E22&lt;0,J22&lt;0,AND(LEN(L22)&gt;0,L22&lt;0)),"ERROR: Negative input",IF(C22&lt;E22,"ERROR: Big SELL must be &gt;= Small BUY",IF(AND(LEN(L22)&gt;0,L22&gt;G22),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N22&lt;0,Q22&lt;0,R22&lt;0),"ERROR: Negative totals",IF(Q22&gt;R22,"ERROR: Rounding broke protection balance",IF(S22&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U22">
+        <f>IF(LEFT(T22,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V22">
         <f>Settings!$B$2*C22/100</f>
         <v/>
       </c>
       <c r="W22">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V22,Settings!$B$5),V22),IF(Settings!$B$9,MROUND(V22,Settings!$B$5),V22))</f>
+        <f>IF(Settings!$B$9,FLOOR(V22,Settings!$B$5),V22)</f>
         <v/>
       </c>
       <c r="X22">
@@ -8880,7 +10104,7 @@
         <v/>
       </c>
       <c r="Y22">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X22,Settings!$B$5),X22),IF(Settings!$B$9,MROUND(X22,Settings!$B$5),X22))</f>
+        <f>IF(Settings!$B$9,CEILING(X22,Settings!$B$5),X22)</f>
         <v/>
       </c>
       <c r="Z22">
@@ -8892,11 +10116,11 @@
         <v/>
       </c>
       <c r="AB22">
-        <f>IF(T22="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA22-Z22)&gt;1E-9),"FIXED",IF(ABS(S22)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T22,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA22-Z22)&gt;1E-9),"FIXED",IF(ABS(S22)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>IF(AB22="FIXED","Close adjusted by SAFE mode",IF(AB22="SAFE","Balance preserved",IF(AB22="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB22="FIXED","Close adjusted by SAFE mode",IF(AB22="SAFE","BUY/SELL balance preserved",IF(AB22="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -8980,12 +10204,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C23&lt;0,E23&lt;0,J23&lt;0,AND(LEN(L23)&gt;0,L23&lt;0)),"ERROR: Negative input",IF(C23&lt;E23,"ERROR: Big SELL must be &gt;= Small BUY",IF(AND(LEN(L23)&gt;0,L23&gt;G23),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N23&lt;0,Q23&lt;0,R23&lt;0),"ERROR: Negative totals",IF(Q23&gt;R23,"ERROR: Rounding broke protection balance",IF(S23&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U23">
+        <f>IF(LEFT(T23,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V23">
         <f>Settings!$B$2*C23/100</f>
         <v/>
       </c>
       <c r="W23">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V23,Settings!$B$5),V23),IF(Settings!$B$9,MROUND(V23,Settings!$B$5),V23))</f>
+        <f>IF(Settings!$B$9,FLOOR(V23,Settings!$B$5),V23)</f>
         <v/>
       </c>
       <c r="X23">
@@ -8993,7 +10221,7 @@
         <v/>
       </c>
       <c r="Y23">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X23,Settings!$B$5),X23),IF(Settings!$B$9,MROUND(X23,Settings!$B$5),X23))</f>
+        <f>IF(Settings!$B$9,CEILING(X23,Settings!$B$5),X23)</f>
         <v/>
       </c>
       <c r="Z23">
@@ -9005,11 +10233,11 @@
         <v/>
       </c>
       <c r="AB23">
-        <f>IF(T23="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA23-Z23)&gt;1E-9),"FIXED",IF(ABS(S23)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T23,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA23-Z23)&gt;1E-9),"FIXED",IF(ABS(S23)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>IF(AB23="FIXED","Close adjusted by SAFE mode",IF(AB23="SAFE","Balance preserved",IF(AB23="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB23="FIXED","Close adjusted by SAFE mode",IF(AB23="SAFE","BUY/SELL balance preserved",IF(AB23="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -9093,12 +10321,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C24&lt;0,E24&lt;0,J24&lt;0,AND(LEN(L24)&gt;0,L24&lt;0)),"ERROR: Negative input",IF(C24&lt;E24,"ERROR: Big SELL must be &gt;= Small BUY",IF(AND(LEN(L24)&gt;0,L24&gt;G24),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N24&lt;0,Q24&lt;0,R24&lt;0),"ERROR: Negative totals",IF(Q24&gt;R24,"ERROR: Rounding broke protection balance",IF(S24&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U24">
+        <f>IF(LEFT(T24,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V24">
         <f>Settings!$B$2*C24/100</f>
         <v/>
       </c>
       <c r="W24">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V24,Settings!$B$5),V24),IF(Settings!$B$9,MROUND(V24,Settings!$B$5),V24))</f>
+        <f>IF(Settings!$B$9,FLOOR(V24,Settings!$B$5),V24)</f>
         <v/>
       </c>
       <c r="X24">
@@ -9106,7 +10338,7 @@
         <v/>
       </c>
       <c r="Y24">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X24,Settings!$B$5),X24),IF(Settings!$B$9,MROUND(X24,Settings!$B$5),X24))</f>
+        <f>IF(Settings!$B$9,CEILING(X24,Settings!$B$5),X24)</f>
         <v/>
       </c>
       <c r="Z24">
@@ -9118,11 +10350,11 @@
         <v/>
       </c>
       <c r="AB24">
-        <f>IF(T24="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA24-Z24)&gt;1E-9),"FIXED",IF(ABS(S24)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T24,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA24-Z24)&gt;1E-9),"FIXED",IF(ABS(S24)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>IF(AB24="FIXED","Close adjusted by SAFE mode",IF(AB24="SAFE","Balance preserved",IF(AB24="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB24="FIXED","Close adjusted by SAFE mode",IF(AB24="SAFE","BUY/SELL balance preserved",IF(AB24="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -9206,12 +10438,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C25&lt;0,E25&lt;0,J25&lt;0,AND(LEN(L25)&gt;0,L25&lt;0)),"ERROR: Negative input",IF(C25&lt;E25,"ERROR: Big SELL must be &gt;= Small BUY",IF(AND(LEN(L25)&gt;0,L25&gt;G25),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N25&lt;0,Q25&lt;0,R25&lt;0),"ERROR: Negative totals",IF(Q25&gt;R25,"ERROR: Rounding broke protection balance",IF(S25&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U25">
+        <f>IF(LEFT(T25,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V25">
         <f>Settings!$B$2*C25/100</f>
         <v/>
       </c>
       <c r="W25">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V25,Settings!$B$5),V25),IF(Settings!$B$9,MROUND(V25,Settings!$B$5),V25))</f>
+        <f>IF(Settings!$B$9,FLOOR(V25,Settings!$B$5),V25)</f>
         <v/>
       </c>
       <c r="X25">
@@ -9219,7 +10455,7 @@
         <v/>
       </c>
       <c r="Y25">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X25,Settings!$B$5),X25),IF(Settings!$B$9,MROUND(X25,Settings!$B$5),X25))</f>
+        <f>IF(Settings!$B$9,CEILING(X25,Settings!$B$5),X25)</f>
         <v/>
       </c>
       <c r="Z25">
@@ -9231,11 +10467,11 @@
         <v/>
       </c>
       <c r="AB25">
-        <f>IF(T25="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA25-Z25)&gt;1E-9),"FIXED",IF(ABS(S25)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T25,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA25-Z25)&gt;1E-9),"FIXED",IF(ABS(S25)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>IF(AB25="FIXED","Close adjusted by SAFE mode",IF(AB25="SAFE","Balance preserved",IF(AB25="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB25="FIXED","Close adjusted by SAFE mode",IF(AB25="SAFE","BUY/SELL balance preserved",IF(AB25="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -9319,12 +10555,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C26&lt;0,E26&lt;0,J26&lt;0,AND(LEN(L26)&gt;0,L26&lt;0)),"ERROR: Negative input",IF(C26&lt;E26,"ERROR: Big SELL must be &gt;= Small BUY",IF(AND(LEN(L26)&gt;0,L26&gt;G26),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N26&lt;0,Q26&lt;0,R26&lt;0),"ERROR: Negative totals",IF(Q26&gt;R26,"ERROR: Rounding broke protection balance",IF(S26&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U26">
+        <f>IF(LEFT(T26,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V26">
         <f>Settings!$B$2*C26/100</f>
         <v/>
       </c>
       <c r="W26">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V26,Settings!$B$5),V26),IF(Settings!$B$9,MROUND(V26,Settings!$B$5),V26))</f>
+        <f>IF(Settings!$B$9,FLOOR(V26,Settings!$B$5),V26)</f>
         <v/>
       </c>
       <c r="X26">
@@ -9332,7 +10572,7 @@
         <v/>
       </c>
       <c r="Y26">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X26,Settings!$B$5),X26),IF(Settings!$B$9,MROUND(X26,Settings!$B$5),X26))</f>
+        <f>IF(Settings!$B$9,CEILING(X26,Settings!$B$5),X26)</f>
         <v/>
       </c>
       <c r="Z26">
@@ -9344,11 +10584,11 @@
         <v/>
       </c>
       <c r="AB26">
-        <f>IF(T26="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA26-Z26)&gt;1E-9),"FIXED",IF(ABS(S26)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T26,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA26-Z26)&gt;1E-9),"FIXED",IF(ABS(S26)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>IF(AB26="FIXED","Close adjusted by SAFE mode",IF(AB26="SAFE","Balance preserved",IF(AB26="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB26="FIXED","Close adjusted by SAFE mode",IF(AB26="SAFE","BUY/SELL balance preserved",IF(AB26="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -9432,12 +10672,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C27&lt;0,E27&lt;0,J27&lt;0,AND(LEN(L27)&gt;0,L27&lt;0)),"ERROR: Negative input",IF(C27&lt;E27,"ERROR: Big SELL must be &gt;= Small BUY",IF(AND(LEN(L27)&gt;0,L27&gt;G27),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N27&lt;0,Q27&lt;0,R27&lt;0),"ERROR: Negative totals",IF(Q27&gt;R27,"ERROR: Rounding broke protection balance",IF(S27&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U27">
+        <f>IF(LEFT(T27,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V27">
         <f>Settings!$B$2*C27/100</f>
         <v/>
       </c>
       <c r="W27">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V27,Settings!$B$5),V27),IF(Settings!$B$9,MROUND(V27,Settings!$B$5),V27))</f>
+        <f>IF(Settings!$B$9,FLOOR(V27,Settings!$B$5),V27)</f>
         <v/>
       </c>
       <c r="X27">
@@ -9445,7 +10689,7 @@
         <v/>
       </c>
       <c r="Y27">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X27,Settings!$B$5),X27),IF(Settings!$B$9,MROUND(X27,Settings!$B$5),X27))</f>
+        <f>IF(Settings!$B$9,CEILING(X27,Settings!$B$5),X27)</f>
         <v/>
       </c>
       <c r="Z27">
@@ -9457,11 +10701,11 @@
         <v/>
       </c>
       <c r="AB27">
-        <f>IF(T27="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA27-Z27)&gt;1E-9),"FIXED",IF(ABS(S27)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T27,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA27-Z27)&gt;1E-9),"FIXED",IF(ABS(S27)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>IF(AB27="FIXED","Close adjusted by SAFE mode",IF(AB27="SAFE","Balance preserved",IF(AB27="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB27="FIXED","Close adjusted by SAFE mode",IF(AB27="SAFE","BUY/SELL balance preserved",IF(AB27="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -9545,12 +10789,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C28&lt;0,E28&lt;0,J28&lt;0,AND(LEN(L28)&gt;0,L28&lt;0)),"ERROR: Negative input",IF(C28&lt;E28,"ERROR: Big SELL must be &gt;= Small BUY",IF(AND(LEN(L28)&gt;0,L28&gt;G28),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N28&lt;0,Q28&lt;0,R28&lt;0),"ERROR: Negative totals",IF(Q28&gt;R28,"ERROR: Rounding broke protection balance",IF(S28&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U28">
+        <f>IF(LEFT(T28,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V28">
         <f>Settings!$B$2*C28/100</f>
         <v/>
       </c>
       <c r="W28">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V28,Settings!$B$5),V28),IF(Settings!$B$9,MROUND(V28,Settings!$B$5),V28))</f>
+        <f>IF(Settings!$B$9,FLOOR(V28,Settings!$B$5),V28)</f>
         <v/>
       </c>
       <c r="X28">
@@ -9558,7 +10806,7 @@
         <v/>
       </c>
       <c r="Y28">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X28,Settings!$B$5),X28),IF(Settings!$B$9,MROUND(X28,Settings!$B$5),X28))</f>
+        <f>IF(Settings!$B$9,CEILING(X28,Settings!$B$5),X28)</f>
         <v/>
       </c>
       <c r="Z28">
@@ -9570,11 +10818,11 @@
         <v/>
       </c>
       <c r="AB28">
-        <f>IF(T28="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA28-Z28)&gt;1E-9),"FIXED",IF(ABS(S28)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T28,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA28-Z28)&gt;1E-9),"FIXED",IF(ABS(S28)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>IF(AB28="FIXED","Close adjusted by SAFE mode",IF(AB28="SAFE","Balance preserved",IF(AB28="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB28="FIXED","Close adjusted by SAFE mode",IF(AB28="SAFE","BUY/SELL balance preserved",IF(AB28="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -9658,12 +10906,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C29&lt;0,E29&lt;0,J29&lt;0,AND(LEN(L29)&gt;0,L29&lt;0)),"ERROR: Negative input",IF(C29&lt;E29,"ERROR: Big SELL must be &gt;= Small BUY",IF(AND(LEN(L29)&gt;0,L29&gt;G29),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N29&lt;0,Q29&lt;0,R29&lt;0),"ERROR: Negative totals",IF(Q29&gt;R29,"ERROR: Rounding broke protection balance",IF(S29&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U29">
+        <f>IF(LEFT(T29,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V29">
         <f>Settings!$B$2*C29/100</f>
         <v/>
       </c>
       <c r="W29">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V29,Settings!$B$5),V29),IF(Settings!$B$9,MROUND(V29,Settings!$B$5),V29))</f>
+        <f>IF(Settings!$B$9,FLOOR(V29,Settings!$B$5),V29)</f>
         <v/>
       </c>
       <c r="X29">
@@ -9671,7 +10923,7 @@
         <v/>
       </c>
       <c r="Y29">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X29,Settings!$B$5),X29),IF(Settings!$B$9,MROUND(X29,Settings!$B$5),X29))</f>
+        <f>IF(Settings!$B$9,CEILING(X29,Settings!$B$5),X29)</f>
         <v/>
       </c>
       <c r="Z29">
@@ -9683,11 +10935,11 @@
         <v/>
       </c>
       <c r="AB29">
-        <f>IF(T29="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA29-Z29)&gt;1E-9),"FIXED",IF(ABS(S29)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T29,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA29-Z29)&gt;1E-9),"FIXED",IF(ABS(S29)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>IF(AB29="FIXED","Close adjusted by SAFE mode",IF(AB29="SAFE","Balance preserved",IF(AB29="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB29="FIXED","Close adjusted by SAFE mode",IF(AB29="SAFE","BUY/SELL balance preserved",IF(AB29="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -9771,12 +11023,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C30&lt;0,E30&lt;0,J30&lt;0,AND(LEN(L30)&gt;0,L30&lt;0)),"ERROR: Negative input",IF(C30&lt;E30,"ERROR: Big SELL must be &gt;= Small BUY",IF(AND(LEN(L30)&gt;0,L30&gt;G30),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N30&lt;0,Q30&lt;0,R30&lt;0),"ERROR: Negative totals",IF(Q30&gt;R30,"ERROR: Rounding broke protection balance",IF(S30&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U30">
+        <f>IF(LEFT(T30,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V30">
         <f>Settings!$B$2*C30/100</f>
         <v/>
       </c>
       <c r="W30">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V30,Settings!$B$5),V30),IF(Settings!$B$9,MROUND(V30,Settings!$B$5),V30))</f>
+        <f>IF(Settings!$B$9,FLOOR(V30,Settings!$B$5),V30)</f>
         <v/>
       </c>
       <c r="X30">
@@ -9784,7 +11040,7 @@
         <v/>
       </c>
       <c r="Y30">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X30,Settings!$B$5),X30),IF(Settings!$B$9,MROUND(X30,Settings!$B$5),X30))</f>
+        <f>IF(Settings!$B$9,CEILING(X30,Settings!$B$5),X30)</f>
         <v/>
       </c>
       <c r="Z30">
@@ -9796,11 +11052,11 @@
         <v/>
       </c>
       <c r="AB30">
-        <f>IF(T30="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA30-Z30)&gt;1E-9),"FIXED",IF(ABS(S30)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T30,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA30-Z30)&gt;1E-9),"FIXED",IF(ABS(S30)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>IF(AB30="FIXED","Close adjusted by SAFE mode",IF(AB30="SAFE","Balance preserved",IF(AB30="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB30="FIXED","Close adjusted by SAFE mode",IF(AB30="SAFE","BUY/SELL balance preserved",IF(AB30="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -9884,12 +11140,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C31&lt;0,E31&lt;0,J31&lt;0,AND(LEN(L31)&gt;0,L31&lt;0)),"ERROR: Negative input",IF(C31&lt;E31,"ERROR: Big SELL must be &gt;= Small BUY",IF(AND(LEN(L31)&gt;0,L31&gt;G31),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N31&lt;0,Q31&lt;0,R31&lt;0),"ERROR: Negative totals",IF(Q31&gt;R31,"ERROR: Rounding broke protection balance",IF(S31&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U31">
+        <f>IF(LEFT(T31,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V31">
         <f>Settings!$B$2*C31/100</f>
         <v/>
       </c>
       <c r="W31">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V31,Settings!$B$5),V31),IF(Settings!$B$9,MROUND(V31,Settings!$B$5),V31))</f>
+        <f>IF(Settings!$B$9,FLOOR(V31,Settings!$B$5),V31)</f>
         <v/>
       </c>
       <c r="X31">
@@ -9897,7 +11157,7 @@
         <v/>
       </c>
       <c r="Y31">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X31,Settings!$B$5),X31),IF(Settings!$B$9,MROUND(X31,Settings!$B$5),X31))</f>
+        <f>IF(Settings!$B$9,CEILING(X31,Settings!$B$5),X31)</f>
         <v/>
       </c>
       <c r="Z31">
@@ -9909,11 +11169,11 @@
         <v/>
       </c>
       <c r="AB31">
-        <f>IF(T31="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA31-Z31)&gt;1E-9),"FIXED",IF(ABS(S31)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T31,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA31-Z31)&gt;1E-9),"FIXED",IF(ABS(S31)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>IF(AB31="FIXED","Close adjusted by SAFE mode",IF(AB31="SAFE","Balance preserved",IF(AB31="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB31="FIXED","Close adjusted by SAFE mode",IF(AB31="SAFE","BUY/SELL balance preserved",IF(AB31="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -9997,12 +11257,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C32&lt;0,E32&lt;0,J32&lt;0,AND(LEN(L32)&gt;0,L32&lt;0)),"ERROR: Negative input",IF(C32&lt;E32,"ERROR: Big SELL must be &gt;= Small BUY",IF(AND(LEN(L32)&gt;0,L32&gt;G32),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N32&lt;0,Q32&lt;0,R32&lt;0),"ERROR: Negative totals",IF(Q32&gt;R32,"ERROR: Rounding broke protection balance",IF(S32&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U32">
+        <f>IF(LEFT(T32,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V32">
         <f>Settings!$B$2*C32/100</f>
         <v/>
       </c>
       <c r="W32">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V32,Settings!$B$5),V32),IF(Settings!$B$9,MROUND(V32,Settings!$B$5),V32))</f>
+        <f>IF(Settings!$B$9,FLOOR(V32,Settings!$B$5),V32)</f>
         <v/>
       </c>
       <c r="X32">
@@ -10010,7 +11274,7 @@
         <v/>
       </c>
       <c r="Y32">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X32,Settings!$B$5),X32),IF(Settings!$B$9,MROUND(X32,Settings!$B$5),X32))</f>
+        <f>IF(Settings!$B$9,CEILING(X32,Settings!$B$5),X32)</f>
         <v/>
       </c>
       <c r="Z32">
@@ -10022,11 +11286,11 @@
         <v/>
       </c>
       <c r="AB32">
-        <f>IF(T32="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA32-Z32)&gt;1E-9),"FIXED",IF(ABS(S32)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T32,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA32-Z32)&gt;1E-9),"FIXED",IF(ABS(S32)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>IF(AB32="FIXED","Close adjusted by SAFE mode",IF(AB32="SAFE","Balance preserved",IF(AB32="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB32="FIXED","Close adjusted by SAFE mode",IF(AB32="SAFE","BUY/SELL balance preserved",IF(AB32="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -10110,12 +11374,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C33&lt;0,E33&lt;0,J33&lt;0,AND(LEN(L33)&gt;0,L33&lt;0)),"ERROR: Negative input",IF(C33&lt;E33,"ERROR: Big SELL must be &gt;= Small BUY",IF(AND(LEN(L33)&gt;0,L33&gt;G33),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N33&lt;0,Q33&lt;0,R33&lt;0),"ERROR: Negative totals",IF(Q33&gt;R33,"ERROR: Rounding broke protection balance",IF(S33&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U33">
+        <f>IF(LEFT(T33,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V33">
         <f>Settings!$B$2*C33/100</f>
         <v/>
       </c>
       <c r="W33">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V33,Settings!$B$5),V33),IF(Settings!$B$9,MROUND(V33,Settings!$B$5),V33))</f>
+        <f>IF(Settings!$B$9,FLOOR(V33,Settings!$B$5),V33)</f>
         <v/>
       </c>
       <c r="X33">
@@ -10123,7 +11391,7 @@
         <v/>
       </c>
       <c r="Y33">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X33,Settings!$B$5),X33),IF(Settings!$B$9,MROUND(X33,Settings!$B$5),X33))</f>
+        <f>IF(Settings!$B$9,CEILING(X33,Settings!$B$5),X33)</f>
         <v/>
       </c>
       <c r="Z33">
@@ -10135,11 +11403,11 @@
         <v/>
       </c>
       <c r="AB33">
-        <f>IF(T33="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA33-Z33)&gt;1E-9),"FIXED",IF(ABS(S33)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T33,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA33-Z33)&gt;1E-9),"FIXED",IF(ABS(S33)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>IF(AB33="FIXED","Close adjusted by SAFE mode",IF(AB33="SAFE","Balance preserved",IF(AB33="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB33="FIXED","Close adjusted by SAFE mode",IF(AB33="SAFE","BUY/SELL balance preserved",IF(AB33="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -10223,12 +11491,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C34&lt;0,E34&lt;0,J34&lt;0,AND(LEN(L34)&gt;0,L34&lt;0)),"ERROR: Negative input",IF(C34&lt;E34,"ERROR: Big SELL must be &gt;= Small BUY",IF(AND(LEN(L34)&gt;0,L34&gt;G34),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N34&lt;0,Q34&lt;0,R34&lt;0),"ERROR: Negative totals",IF(Q34&gt;R34,"ERROR: Rounding broke protection balance",IF(S34&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U34">
+        <f>IF(LEFT(T34,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V34">
         <f>Settings!$B$2*C34/100</f>
         <v/>
       </c>
       <c r="W34">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V34,Settings!$B$5),V34),IF(Settings!$B$9,MROUND(V34,Settings!$B$5),V34))</f>
+        <f>IF(Settings!$B$9,FLOOR(V34,Settings!$B$5),V34)</f>
         <v/>
       </c>
       <c r="X34">
@@ -10236,7 +11508,7 @@
         <v/>
       </c>
       <c r="Y34">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X34,Settings!$B$5),X34),IF(Settings!$B$9,MROUND(X34,Settings!$B$5),X34))</f>
+        <f>IF(Settings!$B$9,CEILING(X34,Settings!$B$5),X34)</f>
         <v/>
       </c>
       <c r="Z34">
@@ -10248,11 +11520,11 @@
         <v/>
       </c>
       <c r="AB34">
-        <f>IF(T34="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA34-Z34)&gt;1E-9),"FIXED",IF(ABS(S34)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T34,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA34-Z34)&gt;1E-9),"FIXED",IF(ABS(S34)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>IF(AB34="FIXED","Close adjusted by SAFE mode",IF(AB34="SAFE","Balance preserved",IF(AB34="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB34="FIXED","Close adjusted by SAFE mode",IF(AB34="SAFE","BUY/SELL balance preserved",IF(AB34="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -10336,12 +11608,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C35&lt;0,E35&lt;0,J35&lt;0,AND(LEN(L35)&gt;0,L35&lt;0)),"ERROR: Negative input",IF(C35&lt;E35,"ERROR: Big SELL must be &gt;= Small BUY",IF(AND(LEN(L35)&gt;0,L35&gt;G35),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N35&lt;0,Q35&lt;0,R35&lt;0),"ERROR: Negative totals",IF(Q35&gt;R35,"ERROR: Rounding broke protection balance",IF(S35&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U35">
+        <f>IF(LEFT(T35,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V35">
         <f>Settings!$B$2*C35/100</f>
         <v/>
       </c>
       <c r="W35">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V35,Settings!$B$5),V35),IF(Settings!$B$9,MROUND(V35,Settings!$B$5),V35))</f>
+        <f>IF(Settings!$B$9,FLOOR(V35,Settings!$B$5),V35)</f>
         <v/>
       </c>
       <c r="X35">
@@ -10349,7 +11625,7 @@
         <v/>
       </c>
       <c r="Y35">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X35,Settings!$B$5),X35),IF(Settings!$B$9,MROUND(X35,Settings!$B$5),X35))</f>
+        <f>IF(Settings!$B$9,CEILING(X35,Settings!$B$5),X35)</f>
         <v/>
       </c>
       <c r="Z35">
@@ -10361,11 +11637,11 @@
         <v/>
       </c>
       <c r="AB35">
-        <f>IF(T35="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA35-Z35)&gt;1E-9),"FIXED",IF(ABS(S35)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T35,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA35-Z35)&gt;1E-9),"FIXED",IF(ABS(S35)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>IF(AB35="FIXED","Close adjusted by SAFE mode",IF(AB35="SAFE","Balance preserved",IF(AB35="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB35="FIXED","Close adjusted by SAFE mode",IF(AB35="SAFE","BUY/SELL balance preserved",IF(AB35="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -10449,12 +11725,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C36&lt;0,E36&lt;0,J36&lt;0,AND(LEN(L36)&gt;0,L36&lt;0)),"ERROR: Negative input",IF(C36&lt;E36,"ERROR: Big SELL must be &gt;= Small BUY",IF(AND(LEN(L36)&gt;0,L36&gt;G36),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N36&lt;0,Q36&lt;0,R36&lt;0),"ERROR: Negative totals",IF(Q36&gt;R36,"ERROR: Rounding broke protection balance",IF(S36&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U36">
+        <f>IF(LEFT(T36,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V36">
         <f>Settings!$B$2*C36/100</f>
         <v/>
       </c>
       <c r="W36">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V36,Settings!$B$5),V36),IF(Settings!$B$9,MROUND(V36,Settings!$B$5),V36))</f>
+        <f>IF(Settings!$B$9,FLOOR(V36,Settings!$B$5),V36)</f>
         <v/>
       </c>
       <c r="X36">
@@ -10462,7 +11742,7 @@
         <v/>
       </c>
       <c r="Y36">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X36,Settings!$B$5),X36),IF(Settings!$B$9,MROUND(X36,Settings!$B$5),X36))</f>
+        <f>IF(Settings!$B$9,CEILING(X36,Settings!$B$5),X36)</f>
         <v/>
       </c>
       <c r="Z36">
@@ -10474,11 +11754,11 @@
         <v/>
       </c>
       <c r="AB36">
-        <f>IF(T36="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA36-Z36)&gt;1E-9),"FIXED",IF(ABS(S36)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T36,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA36-Z36)&gt;1E-9),"FIXED",IF(ABS(S36)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>IF(AB36="FIXED","Close adjusted by SAFE mode",IF(AB36="SAFE","Balance preserved",IF(AB36="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB36="FIXED","Close adjusted by SAFE mode",IF(AB36="SAFE","BUY/SELL balance preserved",IF(AB36="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -10562,12 +11842,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C37&lt;0,E37&lt;0,J37&lt;0,AND(LEN(L37)&gt;0,L37&lt;0)),"ERROR: Negative input",IF(C37&lt;E37,"ERROR: Big SELL must be &gt;= Small BUY",IF(AND(LEN(L37)&gt;0,L37&gt;G37),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N37&lt;0,Q37&lt;0,R37&lt;0),"ERROR: Negative totals",IF(Q37&gt;R37,"ERROR: Rounding broke protection balance",IF(S37&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U37">
+        <f>IF(LEFT(T37,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V37">
         <f>Settings!$B$2*C37/100</f>
         <v/>
       </c>
       <c r="W37">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V37,Settings!$B$5),V37),IF(Settings!$B$9,MROUND(V37,Settings!$B$5),V37))</f>
+        <f>IF(Settings!$B$9,FLOOR(V37,Settings!$B$5),V37)</f>
         <v/>
       </c>
       <c r="X37">
@@ -10575,7 +11859,7 @@
         <v/>
       </c>
       <c r="Y37">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X37,Settings!$B$5),X37),IF(Settings!$B$9,MROUND(X37,Settings!$B$5),X37))</f>
+        <f>IF(Settings!$B$9,CEILING(X37,Settings!$B$5),X37)</f>
         <v/>
       </c>
       <c r="Z37">
@@ -10587,11 +11871,11 @@
         <v/>
       </c>
       <c r="AB37">
-        <f>IF(T37="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA37-Z37)&gt;1E-9),"FIXED",IF(ABS(S37)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T37,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA37-Z37)&gt;1E-9),"FIXED",IF(ABS(S37)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>IF(AB37="FIXED","Close adjusted by SAFE mode",IF(AB37="SAFE","Balance preserved",IF(AB37="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB37="FIXED","Close adjusted by SAFE mode",IF(AB37="SAFE","BUY/SELL balance preserved",IF(AB37="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -10675,12 +11959,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C38&lt;0,E38&lt;0,J38&lt;0,AND(LEN(L38)&gt;0,L38&lt;0)),"ERROR: Negative input",IF(C38&lt;E38,"ERROR: Big SELL must be &gt;= Small BUY",IF(AND(LEN(L38)&gt;0,L38&gt;G38),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N38&lt;0,Q38&lt;0,R38&lt;0),"ERROR: Negative totals",IF(Q38&gt;R38,"ERROR: Rounding broke protection balance",IF(S38&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U38">
+        <f>IF(LEFT(T38,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V38">
         <f>Settings!$B$2*C38/100</f>
         <v/>
       </c>
       <c r="W38">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V38,Settings!$B$5),V38),IF(Settings!$B$9,MROUND(V38,Settings!$B$5),V38))</f>
+        <f>IF(Settings!$B$9,FLOOR(V38,Settings!$B$5),V38)</f>
         <v/>
       </c>
       <c r="X38">
@@ -10688,7 +11976,7 @@
         <v/>
       </c>
       <c r="Y38">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X38,Settings!$B$5),X38),IF(Settings!$B$9,MROUND(X38,Settings!$B$5),X38))</f>
+        <f>IF(Settings!$B$9,CEILING(X38,Settings!$B$5),X38)</f>
         <v/>
       </c>
       <c r="Z38">
@@ -10700,11 +11988,11 @@
         <v/>
       </c>
       <c r="AB38">
-        <f>IF(T38="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA38-Z38)&gt;1E-9),"FIXED",IF(ABS(S38)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T38,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA38-Z38)&gt;1E-9),"FIXED",IF(ABS(S38)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>IF(AB38="FIXED","Close adjusted by SAFE mode",IF(AB38="SAFE","Balance preserved",IF(AB38="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB38="FIXED","Close adjusted by SAFE mode",IF(AB38="SAFE","BUY/SELL balance preserved",IF(AB38="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -10788,12 +12076,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C39&lt;0,E39&lt;0,J39&lt;0,AND(LEN(L39)&gt;0,L39&lt;0)),"ERROR: Negative input",IF(C39&lt;E39,"ERROR: Big SELL must be &gt;= Small BUY",IF(AND(LEN(L39)&gt;0,L39&gt;G39),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N39&lt;0,Q39&lt;0,R39&lt;0),"ERROR: Negative totals",IF(Q39&gt;R39,"ERROR: Rounding broke protection balance",IF(S39&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U39">
+        <f>IF(LEFT(T39,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V39">
         <f>Settings!$B$2*C39/100</f>
         <v/>
       </c>
       <c r="W39">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V39,Settings!$B$5),V39),IF(Settings!$B$9,MROUND(V39,Settings!$B$5),V39))</f>
+        <f>IF(Settings!$B$9,FLOOR(V39,Settings!$B$5),V39)</f>
         <v/>
       </c>
       <c r="X39">
@@ -10801,7 +12093,7 @@
         <v/>
       </c>
       <c r="Y39">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X39,Settings!$B$5),X39),IF(Settings!$B$9,MROUND(X39,Settings!$B$5),X39))</f>
+        <f>IF(Settings!$B$9,CEILING(X39,Settings!$B$5),X39)</f>
         <v/>
       </c>
       <c r="Z39">
@@ -10813,11 +12105,11 @@
         <v/>
       </c>
       <c r="AB39">
-        <f>IF(T39="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA39-Z39)&gt;1E-9),"FIXED",IF(ABS(S39)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T39,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA39-Z39)&gt;1E-9),"FIXED",IF(ABS(S39)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>IF(AB39="FIXED","Close adjusted by SAFE mode",IF(AB39="SAFE","Balance preserved",IF(AB39="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB39="FIXED","Close adjusted by SAFE mode",IF(AB39="SAFE","BUY/SELL balance preserved",IF(AB39="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -10901,12 +12193,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C40&lt;0,E40&lt;0,J40&lt;0,AND(LEN(L40)&gt;0,L40&lt;0)),"ERROR: Negative input",IF(C40&lt;E40,"ERROR: Big SELL must be &gt;= Small BUY",IF(AND(LEN(L40)&gt;0,L40&gt;G40),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N40&lt;0,Q40&lt;0,R40&lt;0),"ERROR: Negative totals",IF(Q40&gt;R40,"ERROR: Rounding broke protection balance",IF(S40&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U40">
+        <f>IF(LEFT(T40,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V40">
         <f>Settings!$B$2*C40/100</f>
         <v/>
       </c>
       <c r="W40">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V40,Settings!$B$5),V40),IF(Settings!$B$9,MROUND(V40,Settings!$B$5),V40))</f>
+        <f>IF(Settings!$B$9,FLOOR(V40,Settings!$B$5),V40)</f>
         <v/>
       </c>
       <c r="X40">
@@ -10914,7 +12210,7 @@
         <v/>
       </c>
       <c r="Y40">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X40,Settings!$B$5),X40),IF(Settings!$B$9,MROUND(X40,Settings!$B$5),X40))</f>
+        <f>IF(Settings!$B$9,CEILING(X40,Settings!$B$5),X40)</f>
         <v/>
       </c>
       <c r="Z40">
@@ -10926,11 +12222,11 @@
         <v/>
       </c>
       <c r="AB40">
-        <f>IF(T40="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA40-Z40)&gt;1E-9),"FIXED",IF(ABS(S40)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T40,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA40-Z40)&gt;1E-9),"FIXED",IF(ABS(S40)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>IF(AB40="FIXED","Close adjusted by SAFE mode",IF(AB40="SAFE","Balance preserved",IF(AB40="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB40="FIXED","Close adjusted by SAFE mode",IF(AB40="SAFE","BUY/SELL balance preserved",IF(AB40="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -11014,12 +12310,16 @@
         <f>IF(Settings!$B$18=FALSE,"OK",IF(OR(NOT(ISNUMBER(Settings!$B$2)),Settings!$B$2&lt;=0),"ERROR: Invalid StartLot",IF(OR(NOT(ISNUMBER(Settings!$B$5)),Settings!$B$5&lt;=0),"ERROR: Invalid LotStep",IF(OR(Settings!$B$4&lt;1,Settings!$B$4&gt;20),"ERROR: Invalid MaxLevels",IF(AND(Settings!$B$10&lt;&gt;"DOWN",Settings!$B$10&lt;&gt;"UP"),"ERROR: Invalid Direction",IF(OR(C41&lt;0,E41&lt;0,J41&lt;0,AND(LEN(L41)&gt;0,L41&lt;0)),"ERROR: Negative input",IF(C41&lt;E41,"ERROR: Big SELL must be &gt;= Small BUY",IF(AND(LEN(L41)&gt;0,L41&gt;G41),"ERROR: ManualClose exceeds remaining Start position",IF(OR(N41&lt;0,Q41&lt;0,R41&lt;0),"ERROR: Negative totals",IF(Q41&gt;R41,"ERROR: Rounding broke protection balance",IF(S41&gt;Settings!$B$8,"WARNING: Skew exceeds recommended limit","OK")))))))))))</f>
         <v/>
       </c>
+      <c r="U41">
+        <f>IF(LEFT(T41,5)="ERROR","Check input/risk","")</f>
+        <v/>
+      </c>
       <c r="V41">
         <f>Settings!$B$2*C41/100</f>
         <v/>
       </c>
       <c r="W41">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,FLOOR(V41,Settings!$B$5),V41),IF(Settings!$B$9,MROUND(V41,Settings!$B$5),V41))</f>
+        <f>IF(Settings!$B$9,FLOOR(V41,Settings!$B$5),V41)</f>
         <v/>
       </c>
       <c r="X41">
@@ -11027,7 +12327,7 @@
         <v/>
       </c>
       <c r="Y41">
-        <f>IF(Settings!$B$17,IF(Settings!$B$9,CEILING(X41,Settings!$B$5),X41),IF(Settings!$B$9,MROUND(X41,Settings!$B$5),X41))</f>
+        <f>IF(Settings!$B$9,CEILING(X41,Settings!$B$5),X41)</f>
         <v/>
       </c>
       <c r="Z41">
@@ -11039,11 +12339,11 @@
         <v/>
       </c>
       <c r="AB41">
-        <f>IF(T41="ERROR: Rounding broke protection balance","ERROR",IF(AND(Settings!$B$17,ABS(AA41-Z41)&gt;1E-9),"FIXED",IF(ABS(S41)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
+        <f>IF(LEFT(T41,5)="ERROR","ERROR",IF(AND(Settings!$B$17,ABS(AA41-Z41)&gt;1E-9),"FIXED",IF(ABS(S41)&lt;=Settings!$B$7,"SAFE","WARNING")))</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>IF(AB41="FIXED","Close adjusted by SAFE mode",IF(AB41="SAFE","Balance preserved",IF(AB41="WARNING","Near protection boundary","Protection broken")))</f>
+        <f>IF(AB41="FIXED","Close adjusted by SAFE mode",IF(AB41="SAFE","BUY/SELL balance preserved",IF(AB41="WARNING","Near protection boundary","Protection broken")))</f>
         <v/>
       </c>
     </row>
@@ -11072,106 +12372,101 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Parameter</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>StartLot</t>
-        </is>
-      </c>
-      <c r="B2">
-        <f>Settings!B2</f>
-        <v/>
+          <t>V3 Dashboard Summary</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>StartLot</t>
         </is>
       </c>
       <c r="B3">
-        <f>Settings!B10</f>
+        <f>Settings!B2</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MaxLevels</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="B4">
-        <f>Settings!B4</f>
+        <f>Settings!B10</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Final Total BUY %</t>
+          <t>Adaptive Step</t>
         </is>
       </c>
       <c r="B5">
-        <f>IF(Settings!B10="DOWN",INDEX(DownTrend!Q:Q,Settings!B4+3),INDEX(UpTrend!R:R,Settings!B4+3))</f>
+        <f>MarketModel!B16</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Final Total SELL %</t>
+          <t>ATR Regime</t>
         </is>
       </c>
       <c r="B6">
-        <f>IF(Settings!B10="DOWN",INDEX(DownTrend!R:R,Settings!B4+3),INDEX(UpTrend!Q:Q,Settings!B4+3))</f>
+        <f>MarketModel!B11</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Final Skew %</t>
+          <t>Margin Load</t>
         </is>
       </c>
       <c r="B7">
-        <f>ABS(B5-B4)</f>
+        <f>MarginControl!B13</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Final Start Remaining %</t>
+          <t>Risk Score</t>
         </is>
       </c>
       <c r="B8">
-        <f>IF(Settings!B10="DOWN",INDEX(DownTrend!N:N,Settings!B4+3),INDEX(UpTrend!N:N,Settings!B4+3))</f>
+        <f>RiskDashboard!B2</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Final Status</t>
+          <t>Max Safe Levels</t>
         </is>
       </c>
       <c r="B9">
-        <f>IF(Settings!B10="DOWN",INDEX(DownTrend!T:T,Settings!B4+3),INDEX(UpTrend!T:T,Settings!B4+3))</f>
+        <f>MarginControl!B17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Survival Probability</t>
+        </is>
+      </c>
+      <c r="B10">
+        <f>RiskDashboard!B5</f>
         <v/>
       </c>
     </row>
@@ -11187,106 +12482,90 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Result</t>
+          <t>Checks</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Invalid StartLot</t>
+          <t>Big&gt;=Small</t>
         </is>
       </c>
       <c r="B2">
-        <f>IF(OR(NOT(ISNUMBER(Settings!B2)),Settings!B2&lt;=0),"ERROR","OK")</f>
+        <f>IF(SUMPRODUCT(--(DownTrend!C3:C41&lt;DownTrend!E3:E41))+SUMPRODUCT(--(UpTrend!C3:C41&lt;UpTrend!E3:E41))&gt;0,"ERROR","OK")</f>
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Invalid LotStep</t>
+          <t>TotalBUY&lt;=TotalSELL Down</t>
         </is>
       </c>
       <c r="B3">
-        <f>IF(OR(NOT(ISNUMBER(Settings!B5)),Settings!B5&lt;=0),"ERROR","OK")</f>
+        <f>IF(SUMPRODUCT(--(DownTrend!Q3:Q41&gt;DownTrend!R3:R41))&gt;0,"ERROR","OK")</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Invalid Direction</t>
+          <t>TotalSELL&lt;=TotalBUY Up</t>
         </is>
       </c>
       <c r="B4">
-        <f>IF(AND(Settings!B10&lt;&gt;"DOWN",Settings!B10&lt;&gt;"UP"),"ERROR","OK")</f>
+        <f>IF(SUMPRODUCT(--(UpTrend!Q3:Q41&gt;UpTrend!R3:R41))&gt;0,"ERROR","OK")</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Big&gt;=Small Down/Up</t>
+          <t>SAFE rounding preserved</t>
         </is>
       </c>
       <c r="B5">
-        <f>IF(SUMPRODUCT(--(DownTrend!C3:C41&lt;DownTrend!E3:E41))+SUMPRODUCT(--(UpTrend!C3:C41&lt;UpTrend!E3:E41))&gt;0,"ERROR","OK")</f>
+        <f>IF(OR(COUNTIF(DownTrend!AB3:AB41,"ERROR")&gt;0,COUNTIF(UpTrend!AB3:AB41,"ERROR")&gt;0),"ERROR","OK")</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TotalBUY&lt;=TotalSELL Down</t>
+          <t>Invalid StartLot</t>
         </is>
       </c>
       <c r="B6">
-        <f>IF(SUMPRODUCT(--(DownTrend!Q3:Q41&gt;DownTrend!R3:R41))&gt;0,"ERROR","OK")</f>
+        <f>IF(OR(NOT(ISNUMBER(Settings!B2)),Settings!B2&lt;=0),"ERROR","OK")</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TotalSELL&lt;=TotalBUY Up</t>
+          <t>Invalid LotStep</t>
         </is>
       </c>
       <c r="B7">
-        <f>IF(SUMPRODUCT(--(UpTrend!Q3:Q41&gt;UpTrend!R3:R41))&gt;0,"ERROR","OK")</f>
+        <f>IF(OR(NOT(ISNUMBER(Settings!B5)),Settings!B5&lt;=0),"ERROR","OK")</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SAFE rounding preserved</t>
+          <t>Invalid Direction</t>
         </is>
       </c>
       <c r="B8">
-        <f>IF(OR(COUNTIF(DownTrend!AB3:AB41,"ERROR")&gt;0,COUNTIF(UpTrend!AB3:AB41,"ERROR")&gt;0),"ERROR","OK")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Negative values</t>
-        </is>
-      </c>
-      <c r="B9">
-        <f>IF(OR(MIN(DownTrend!N3:N41)&lt;0,MIN(UpTrend!N3:N41)&lt;0,MIN(DownTrend!Q3:R41)&lt;0,MIN(UpTrend!Q3:R41)&lt;0),"ERROR","OK")</f>
+        <f>IF(AND(Settings!B10&lt;&gt;"DOWN",Settings!B10&lt;&gt;"UP"),"ERROR","OK")</f>
         <v/>
       </c>
     </row>
@@ -11307,8 +12586,851 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>v2: Risk-Safe Rounding + Full Input Validation enabled.</t>
-        </is>
+          <t>V3: Adaptive probabilistic recovery engine prototype with risk dashboard.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Market Model Inputs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CurrentPrice</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ATR(14)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ATR Multiplier</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Swap</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Commission</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Daily Volatility</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Weekly Volatility</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Trend Strength</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Volatility Regime</t>
+        </is>
+      </c>
+      <c r="B11">
+        <f>IF(B3&lt;60,"LOW_VOL",IF(B3&lt;120,"NORMAL",IF(B3&lt;200,"HIGH_VOL","EXTREME")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Symbol Digits</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Point Value</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Contract Size</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Adaptive Step</t>
+        </is>
+      </c>
+      <c r="B16">
+        <f>B3*B4</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adaptive Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CurrentSkew</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>LockWidth</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>DistanceFromAverage</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MarginLoad</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>RecoveryPressure</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TrendRisk</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>RollbackProbability</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>DD%</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>DecayK</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BaseBig</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>BaseSmall</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>RiskFactor</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Level</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>DynamicBig%</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>DynamicSmall%</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>DynamicTargetSkew%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17">
+        <f>MAX(1,$B$11*EXP(-$B$10*A17)*$B$12)</f>
+        <v/>
+      </c>
+      <c r="C17">
+        <f>MAX(1,$B$12*($B$6/50)*MAX(0.5,1+$B$2/100))</f>
+        <v/>
+      </c>
+      <c r="D17">
+        <f>MIN(30,MAX(5,5+$B$6/5+$B$4/10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18">
+        <f>MAX(1,$B$11*EXP(-$B$10*A18)*$B$12)</f>
+        <v/>
+      </c>
+      <c r="C18">
+        <f>MAX(1,$B$12*($B$6/50)*MAX(0.5,1+$B$2/100))</f>
+        <v/>
+      </c>
+      <c r="D18">
+        <f>MIN(30,MAX(5,5+$B$6/5+$B$4/10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>3</v>
+      </c>
+      <c r="B19">
+        <f>MAX(1,$B$11*EXP(-$B$10*A19)*$B$12)</f>
+        <v/>
+      </c>
+      <c r="C19">
+        <f>MAX(1,$B$12*($B$6/50)*MAX(0.5,1+$B$2/100))</f>
+        <v/>
+      </c>
+      <c r="D19">
+        <f>MIN(30,MAX(5,5+$B$6/5+$B$4/10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>4</v>
+      </c>
+      <c r="B20">
+        <f>MAX(1,$B$11*EXP(-$B$10*A20)*$B$12)</f>
+        <v/>
+      </c>
+      <c r="C20">
+        <f>MAX(1,$B$12*($B$6/50)*MAX(0.5,1+$B$2/100))</f>
+        <v/>
+      </c>
+      <c r="D20">
+        <f>MIN(30,MAX(5,5+$B$6/5+$B$4/10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>5</v>
+      </c>
+      <c r="B21">
+        <f>MAX(1,$B$11*EXP(-$B$10*A21)*$B$12)</f>
+        <v/>
+      </c>
+      <c r="C21">
+        <f>MAX(1,$B$12*($B$6/50)*MAX(0.5,1+$B$2/100))</f>
+        <v/>
+      </c>
+      <c r="D21">
+        <f>MIN(30,MAX(5,5+$B$6/5+$B$4/10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>6</v>
+      </c>
+      <c r="B22">
+        <f>MAX(1,$B$11*EXP(-$B$10*A22)*$B$12)</f>
+        <v/>
+      </c>
+      <c r="C22">
+        <f>MAX(1,$B$12*($B$6/50)*MAX(0.5,1+$B$2/100))</f>
+        <v/>
+      </c>
+      <c r="D22">
+        <f>MIN(30,MAX(5,5+$B$6/5+$B$4/10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>7</v>
+      </c>
+      <c r="B23">
+        <f>MAX(1,$B$11*EXP(-$B$10*A23)*$B$12)</f>
+        <v/>
+      </c>
+      <c r="C23">
+        <f>MAX(1,$B$12*($B$6/50)*MAX(0.5,1+$B$2/100))</f>
+        <v/>
+      </c>
+      <c r="D23">
+        <f>MIN(30,MAX(5,5+$B$6/5+$B$4/10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>8</v>
+      </c>
+      <c r="B24">
+        <f>MAX(1,$B$11*EXP(-$B$10*A24)*$B$12)</f>
+        <v/>
+      </c>
+      <c r="C24">
+        <f>MAX(1,$B$12*($B$6/50)*MAX(0.5,1+$B$2/100))</f>
+        <v/>
+      </c>
+      <c r="D24">
+        <f>MIN(30,MAX(5,5+$B$6/5+$B$4/10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>9</v>
+      </c>
+      <c r="B25">
+        <f>MAX(1,$B$11*EXP(-$B$10*A25)*$B$12)</f>
+        <v/>
+      </c>
+      <c r="C25">
+        <f>MAX(1,$B$12*($B$6/50)*MAX(0.5,1+$B$2/100))</f>
+        <v/>
+      </c>
+      <c r="D25">
+        <f>MIN(30,MAX(5,5+$B$6/5+$B$4/10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>10</v>
+      </c>
+      <c r="B26">
+        <f>MAX(1,$B$11*EXP(-$B$10*A26)*$B$12)</f>
+        <v/>
+      </c>
+      <c r="C26">
+        <f>MAX(1,$B$12*($B$6/50)*MAX(0.5,1+$B$2/100))</f>
+        <v/>
+      </c>
+      <c r="D26">
+        <f>MIN(30,MAX(5,5+$B$6/5+$B$4/10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>11</v>
+      </c>
+      <c r="B27">
+        <f>MAX(1,$B$11*EXP(-$B$10*A27)*$B$12)</f>
+        <v/>
+      </c>
+      <c r="C27">
+        <f>MAX(1,$B$12*($B$6/50)*MAX(0.5,1+$B$2/100))</f>
+        <v/>
+      </c>
+      <c r="D27">
+        <f>MIN(30,MAX(5,5+$B$6/5+$B$4/10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>12</v>
+      </c>
+      <c r="B28">
+        <f>MAX(1,$B$11*EXP(-$B$10*A28)*$B$12)</f>
+        <v/>
+      </c>
+      <c r="C28">
+        <f>MAX(1,$B$12*($B$6/50)*MAX(0.5,1+$B$2/100))</f>
+        <v/>
+      </c>
+      <c r="D28">
+        <f>MIN(30,MAX(5,5+$B$6/5+$B$4/10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>13</v>
+      </c>
+      <c r="B29">
+        <f>MAX(1,$B$11*EXP(-$B$10*A29)*$B$12)</f>
+        <v/>
+      </c>
+      <c r="C29">
+        <f>MAX(1,$B$12*($B$6/50)*MAX(0.5,1+$B$2/100))</f>
+        <v/>
+      </c>
+      <c r="D29">
+        <f>MIN(30,MAX(5,5+$B$6/5+$B$4/10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>14</v>
+      </c>
+      <c r="B30">
+        <f>MAX(1,$B$11*EXP(-$B$10*A30)*$B$12)</f>
+        <v/>
+      </c>
+      <c r="C30">
+        <f>MAX(1,$B$12*($B$6/50)*MAX(0.5,1+$B$2/100))</f>
+        <v/>
+      </c>
+      <c r="D30">
+        <f>MIN(30,MAX(5,5+$B$6/5+$B$4/10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>15</v>
+      </c>
+      <c r="B31">
+        <f>MAX(1,$B$11*EXP(-$B$10*A31)*$B$12)</f>
+        <v/>
+      </c>
+      <c r="C31">
+        <f>MAX(1,$B$12*($B$6/50)*MAX(0.5,1+$B$2/100))</f>
+        <v/>
+      </c>
+      <c r="D31">
+        <f>MIN(30,MAX(5,5+$B$6/5+$B$4/10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>16</v>
+      </c>
+      <c r="B32">
+        <f>MAX(1,$B$11*EXP(-$B$10*A32)*$B$12)</f>
+        <v/>
+      </c>
+      <c r="C32">
+        <f>MAX(1,$B$12*($B$6/50)*MAX(0.5,1+$B$2/100))</f>
+        <v/>
+      </c>
+      <c r="D32">
+        <f>MIN(30,MAX(5,5+$B$6/5+$B$4/10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>17</v>
+      </c>
+      <c r="B33">
+        <f>MAX(1,$B$11*EXP(-$B$10*A33)*$B$12)</f>
+        <v/>
+      </c>
+      <c r="C33">
+        <f>MAX(1,$B$12*($B$6/50)*MAX(0.5,1+$B$2/100))</f>
+        <v/>
+      </c>
+      <c r="D33">
+        <f>MIN(30,MAX(5,5+$B$6/5+$B$4/10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>18</v>
+      </c>
+      <c r="B34">
+        <f>MAX(1,$B$11*EXP(-$B$10*A34)*$B$12)</f>
+        <v/>
+      </c>
+      <c r="C34">
+        <f>MAX(1,$B$12*($B$6/50)*MAX(0.5,1+$B$2/100))</f>
+        <v/>
+      </c>
+      <c r="D34">
+        <f>MIN(30,MAX(5,5+$B$6/5+$B$4/10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>19</v>
+      </c>
+      <c r="B35">
+        <f>MAX(1,$B$11*EXP(-$B$10*A35)*$B$12)</f>
+        <v/>
+      </c>
+      <c r="C35">
+        <f>MAX(1,$B$12*($B$6/50)*MAX(0.5,1+$B$2/100))</f>
+        <v/>
+      </c>
+      <c r="D35">
+        <f>MIN(30,MAX(5,5+$B$6/5+$B$4/10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36">
+        <f>MAX(1,$B$11*EXP(-$B$10*A36)*$B$12)</f>
+        <v/>
+      </c>
+      <c r="C36">
+        <f>MAX(1,$B$12*($B$6/50)*MAX(0.5,1+$B$2/100))</f>
+        <v/>
+      </c>
+      <c r="D36">
+        <f>MIN(30,MAX(5,5+$B$6/5+$B$4/10))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Margin Control</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Balance</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>9400</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FreeMargin</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Leverage</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MarginPerLot</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>MarginCallLevel</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>StopOutLevel</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>UsedMargin</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NextLevelLot</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>RequiredMargin</t>
+        </is>
+      </c>
+      <c r="B12">
+        <f>B9*B5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MarginLoad%</t>
+        </is>
+      </c>
+      <c r="B13">
+        <f>B8/B3*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>FreeMarginAfterNextLevel</t>
+        </is>
+      </c>
+      <c r="B14">
+        <f>B4-B12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>WorstCaseMargin</t>
+        </is>
+      </c>
+      <c r="B15">
+        <f>B8+B12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>MarginStress</t>
+        </is>
+      </c>
+      <c r="B16">
+        <f>IF(B13&lt;30,"SAFE",IF(B13&lt;50,"NORMAL",IF(B13&lt;70,"WARNING",IF(B13&lt;90,"DANGER","CRITICAL"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>MaxSafeLevels</t>
+        </is>
+      </c>
+      <c r="B17">
+        <f>MAX(1,INT(B4/B12))</f>
+        <v/>
       </c>
     </row>
   </sheetData>
